--- a/.doc/官方手册/引脚映射表.xlsx
+++ b/.doc/官方手册/引脚映射表.xlsx
@@ -8,16 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\itgz2\Desktop\BetaRobot\.doc\官方手册\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{230C6DA1-02F6-4C47-B570-C1B73C88A823}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC764761-503E-4A48-B4C2-6576AE2DC394}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DM_MC02" sheetId="1" r:id="rId1"/>
-    <sheet name="DJI_C" sheetId="2" r:id="rId2"/>
+    <sheet name="DJI_C" sheetId="3" r:id="rId2"/>
+    <sheet name="DJI_A" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">DJI_C!$A$1:$G$141</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">DJI_A!$A$1:$F$141</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">DJI_C!$D$1:$D$141</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">DM_MC02!$A$1:$G$81</definedName>
   </definedNames>
   <calcPr calcId="0"/>
@@ -25,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="739" uniqueCount="293">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1175" uniqueCount="324">
   <si>
     <t>Port-Pin</t>
   </si>
@@ -36,15 +38,63 @@
     <t>外设细节</t>
   </si>
   <si>
-    <t>硬件</t>
-  </si>
-  <si>
     <t>CubeMX配置</t>
   </si>
   <si>
     <t>PA00</t>
   </si>
   <si>
+    <t>TIM2</t>
+  </si>
+  <si>
+    <t>CH1</t>
+  </si>
+  <si>
+    <t>PWM</t>
+  </si>
+  <si>
+    <t>168MHZ/(55+1)*(59999)=50HZ</t>
+  </si>
+  <si>
+    <t>PA01</t>
+  </si>
+  <si>
+    <t>CH2</t>
+  </si>
+  <si>
+    <t>PA02</t>
+  </si>
+  <si>
+    <t>CH3</t>
+  </si>
+  <si>
+    <t>PA03</t>
+  </si>
+  <si>
+    <t>CH4</t>
+  </si>
+  <si>
+    <t>PA04</t>
+  </si>
+  <si>
+    <t>DAC</t>
+  </si>
+  <si>
+    <t>OUT1</t>
+  </si>
+  <si>
+    <t>EX</t>
+  </si>
+  <si>
+    <t>PA05</t>
+  </si>
+  <si>
+    <t>OUT2</t>
+  </si>
+  <si>
+    <t>PA06</t>
+  </si>
+  <si>
     <t>GPIO</t>
   </si>
   <si>
@@ -54,815 +104,811 @@
     <t>KEY</t>
   </si>
   <si>
-    <t>用户按键</t>
-  </si>
-  <si>
-    <t>PA01</t>
-  </si>
-  <si>
-    <t>PA02</t>
-  </si>
-  <si>
-    <t>PA03</t>
-  </si>
-  <si>
-    <t>PA04</t>
+    <t>PA07</t>
   </si>
   <si>
     <t>OUT</t>
   </si>
   <si>
+    <t>OLED</t>
+  </si>
+  <si>
+    <t>MOSI</t>
+  </si>
+  <si>
+    <t>PA08</t>
+  </si>
+  <si>
+    <t>I2C3</t>
+  </si>
+  <si>
+    <t>SCL</t>
+  </si>
+  <si>
+    <t>IST8310</t>
+  </si>
+  <si>
+    <t>PA09</t>
+  </si>
+  <si>
+    <t>TIM1</t>
+  </si>
+  <si>
+    <t>PA10</t>
+  </si>
+  <si>
+    <t>USB</t>
+  </si>
+  <si>
+    <t>OTG_FS_ID</t>
+  </si>
+  <si>
+    <t>PA11</t>
+  </si>
+  <si>
+    <t>OTG_FS_DM</t>
+  </si>
+  <si>
+    <t>PA12</t>
+  </si>
+  <si>
+    <t>OTG_FS_DP</t>
+  </si>
+  <si>
+    <t>PA13</t>
+  </si>
+  <si>
+    <t>SW</t>
+  </si>
+  <si>
+    <t>DIO</t>
+  </si>
+  <si>
+    <t>DEBUG</t>
+  </si>
+  <si>
+    <t>PA14</t>
+  </si>
+  <si>
+    <t>CLK</t>
+  </si>
+  <si>
+    <t>PA15</t>
+  </si>
+  <si>
+    <t>PB00</t>
+  </si>
+  <si>
+    <t>ADC1</t>
+  </si>
+  <si>
+    <t>IN8</t>
+  </si>
+  <si>
+    <t>PB01</t>
+  </si>
+  <si>
+    <t>IN9</t>
+  </si>
+  <si>
+    <t>PB02</t>
+  </si>
+  <si>
+    <t>PB03</t>
+  </si>
+  <si>
+    <t>PB04</t>
+  </si>
+  <si>
+    <t>PB05</t>
+  </si>
+  <si>
+    <t>TIM3</t>
+  </si>
+  <si>
+    <t>加热</t>
+  </si>
+  <si>
+    <t>PB06</t>
+  </si>
+  <si>
+    <t>PB07</t>
+  </si>
+  <si>
+    <t>USART1</t>
+  </si>
+  <si>
+    <t>RX</t>
+  </si>
+  <si>
+    <t>UART1</t>
+  </si>
+  <si>
+    <t>PB08</t>
+  </si>
+  <si>
+    <t>INT</t>
+  </si>
+  <si>
+    <t>PB09</t>
+  </si>
+  <si>
+    <t>DC</t>
+  </si>
+  <si>
+    <t>PB10</t>
+  </si>
+  <si>
+    <t>RST</t>
+  </si>
+  <si>
+    <t>PB11</t>
+  </si>
+  <si>
+    <t>PB12</t>
+  </si>
+  <si>
+    <t>CAN2</t>
+  </si>
+  <si>
+    <t>PB13</t>
+  </si>
+  <si>
+    <t>TX</t>
+  </si>
+  <si>
+    <t>PB14</t>
+  </si>
+  <si>
+    <t>I/O</t>
+  </si>
+  <si>
+    <t>PB15</t>
+  </si>
+  <si>
+    <t>PC00</t>
+  </si>
+  <si>
+    <t>IN10</t>
+  </si>
+  <si>
+    <t>PC01</t>
+  </si>
+  <si>
+    <t>IN11</t>
+  </si>
+  <si>
+    <t>PC02</t>
+  </si>
+  <si>
+    <t>IN12</t>
+  </si>
+  <si>
+    <t>PC03</t>
+  </si>
+  <si>
+    <t>IN13</t>
+  </si>
+  <si>
+    <t>PC04</t>
+  </si>
+  <si>
+    <t>IN14</t>
+  </si>
+  <si>
+    <t>PC05</t>
+  </si>
+  <si>
+    <t>IN15</t>
+  </si>
+  <si>
+    <t>PC06</t>
+  </si>
+  <si>
+    <t>PC07</t>
+  </si>
+  <si>
+    <t>PC08</t>
+  </si>
+  <si>
+    <t>SDIO</t>
+  </si>
+  <si>
+    <t>D0</t>
+  </si>
+  <si>
+    <t>SD卡</t>
+  </si>
+  <si>
+    <t>PC09</t>
+  </si>
+  <si>
+    <t>SDA</t>
+  </si>
+  <si>
+    <t>PC10</t>
+  </si>
+  <si>
+    <t>D2</t>
+  </si>
+  <si>
+    <t>PC11</t>
+  </si>
+  <si>
+    <t>D3</t>
+  </si>
+  <si>
+    <t>PC12</t>
+  </si>
+  <si>
+    <t>CK</t>
+  </si>
+  <si>
+    <t>PC13</t>
+  </si>
+  <si>
+    <t>PC14</t>
+  </si>
+  <si>
+    <t>PC15</t>
+  </si>
+  <si>
+    <t>PD00</t>
+  </si>
+  <si>
+    <t>CAN1</t>
+  </si>
+  <si>
+    <t>PD01</t>
+  </si>
+  <si>
+    <t>PD02</t>
+  </si>
+  <si>
+    <t>CMD</t>
+  </si>
+  <si>
+    <t>PD03</t>
+  </si>
+  <si>
+    <t>PD04</t>
+  </si>
+  <si>
+    <t>PD05</t>
+  </si>
+  <si>
+    <t>USART2</t>
+  </si>
+  <si>
+    <t>UART2</t>
+  </si>
+  <si>
+    <t>PD06</t>
+  </si>
+  <si>
+    <t>PD07</t>
+  </si>
+  <si>
+    <t>PD08</t>
+  </si>
+  <si>
+    <t>USART3</t>
+  </si>
+  <si>
+    <t>UART3</t>
+  </si>
+  <si>
+    <t>PD09</t>
+  </si>
+  <si>
+    <t>PD10</t>
+  </si>
+  <si>
+    <t>PD11</t>
+  </si>
+  <si>
+    <t>PD12</t>
+  </si>
+  <si>
+    <t>TIM4</t>
+  </si>
+  <si>
+    <t>PD13</t>
+  </si>
+  <si>
+    <t>PD14</t>
+  </si>
+  <si>
+    <t>PD15</t>
+  </si>
+  <si>
+    <t>PE00</t>
+  </si>
+  <si>
+    <t>UART8</t>
+  </si>
+  <si>
+    <t>PE01</t>
+  </si>
+  <si>
+    <t>PE02</t>
+  </si>
+  <si>
+    <t>RSTN</t>
+  </si>
+  <si>
+    <t>PE03</t>
+  </si>
+  <si>
+    <t>DRDY</t>
+  </si>
+  <si>
+    <t>PE04</t>
+  </si>
+  <si>
+    <t>SPI4</t>
+  </si>
+  <si>
+    <t>NSS</t>
+  </si>
+  <si>
+    <t>PE05</t>
+  </si>
+  <si>
+    <t>MISO</t>
+  </si>
+  <si>
+    <t>PE06</t>
+  </si>
+  <si>
+    <t>PE07</t>
+  </si>
+  <si>
+    <t>UART7</t>
+  </si>
+  <si>
+    <t>PE08</t>
+  </si>
+  <si>
+    <t>PE09</t>
+  </si>
+  <si>
+    <t>PE10</t>
+  </si>
+  <si>
+    <t>PE11</t>
+  </si>
+  <si>
+    <t>LED</t>
+  </si>
+  <si>
+    <t>LED_R</t>
+  </si>
+  <si>
+    <t>PE12</t>
+  </si>
+  <si>
+    <t>SCK</t>
+  </si>
+  <si>
+    <t>PE13</t>
+  </si>
+  <si>
+    <t>PE14</t>
+  </si>
+  <si>
+    <t>PE15</t>
+  </si>
+  <si>
+    <t>PF00</t>
+  </si>
+  <si>
+    <t>I2C2</t>
+  </si>
+  <si>
+    <t>PF01</t>
+  </si>
+  <si>
+    <t>PF02</t>
+  </si>
+  <si>
+    <t>PF03</t>
+  </si>
+  <si>
+    <t>ADC3</t>
+  </si>
+  <si>
+    <t>PF04</t>
+  </si>
+  <si>
+    <t>PF05</t>
+  </si>
+  <si>
+    <t>PF06</t>
+  </si>
+  <si>
+    <t>SPI5</t>
+  </si>
+  <si>
+    <t>PF07</t>
+  </si>
+  <si>
+    <t>PF08</t>
+  </si>
+  <si>
+    <t>PF09</t>
+  </si>
+  <si>
+    <t>PF10</t>
+  </si>
+  <si>
+    <t>ADC_BAT</t>
+  </si>
+  <si>
+    <t>PF11</t>
+  </si>
+  <si>
+    <t>PF12</t>
+  </si>
+  <si>
+    <t>PF13</t>
+  </si>
+  <si>
+    <t>PF14</t>
+  </si>
+  <si>
+    <t>LED_G</t>
+  </si>
+  <si>
+    <t>PF15</t>
+  </si>
+  <si>
+    <t>PG00</t>
+  </si>
+  <si>
+    <t>PG01</t>
+  </si>
+  <si>
+    <t>PG02</t>
+  </si>
+  <si>
+    <t>PG03</t>
+  </si>
+  <si>
+    <t>PG04</t>
+  </si>
+  <si>
+    <t>PG05</t>
+  </si>
+  <si>
+    <t>PG06</t>
+  </si>
+  <si>
+    <t>PG07</t>
+  </si>
+  <si>
+    <t>PG08</t>
+  </si>
+  <si>
+    <t>PG09</t>
+  </si>
+  <si>
+    <t>USART6</t>
+  </si>
+  <si>
+    <t>UART6</t>
+  </si>
+  <si>
+    <t>PG10</t>
+  </si>
+  <si>
+    <t>PG11</t>
+  </si>
+  <si>
+    <t>PG12</t>
+  </si>
+  <si>
+    <t>PG13</t>
+  </si>
+  <si>
+    <t>激光</t>
+  </si>
+  <si>
+    <t>PG14</t>
+  </si>
+  <si>
+    <t>PG15</t>
+  </si>
+  <si>
+    <t>PH00</t>
+  </si>
+  <si>
+    <t>RCC</t>
+  </si>
+  <si>
+    <t>PH01</t>
+  </si>
+  <si>
+    <t>PH02</t>
+  </si>
+  <si>
+    <t>POWER</t>
+  </si>
+  <si>
+    <t>PH03</t>
+  </si>
+  <si>
+    <t>PH04</t>
+  </si>
+  <si>
+    <t>PH05</t>
+  </si>
+  <si>
+    <t>PH06</t>
+  </si>
+  <si>
+    <t>TIM12</t>
+  </si>
+  <si>
+    <t>蜂鸣器</t>
+  </si>
+  <si>
+    <t>84MHZ/(0+1)*(20999+1)=4KHZ</t>
+  </si>
+  <si>
+    <t>PH07</t>
+  </si>
+  <si>
+    <t>PH08</t>
+  </si>
+  <si>
+    <t>PH09</t>
+  </si>
+  <si>
+    <t>PH10</t>
+  </si>
+  <si>
+    <t>TIM5</t>
+  </si>
+  <si>
+    <t>LED_B</t>
+  </si>
+  <si>
+    <t>PH11</t>
+  </si>
+  <si>
+    <t>PH12</t>
+  </si>
+  <si>
+    <t>PH13</t>
+  </si>
+  <si>
+    <t>PH14</t>
+  </si>
+  <si>
+    <t>PH15</t>
+  </si>
+  <si>
+    <t>PI00</t>
+  </si>
+  <si>
+    <t>PI01</t>
+  </si>
+  <si>
+    <t>PI02</t>
+  </si>
+  <si>
+    <t>TIM8</t>
+  </si>
+  <si>
+    <t>PI03</t>
+  </si>
+  <si>
+    <t>PI04</t>
+  </si>
+  <si>
+    <t>PI05</t>
+  </si>
+  <si>
+    <t>PI06</t>
+  </si>
+  <si>
+    <t>PI07</t>
+  </si>
+  <si>
+    <t>PI08</t>
+  </si>
+  <si>
+    <t>PI09</t>
+  </si>
+  <si>
+    <t>EXTI</t>
+  </si>
+  <si>
+    <t>PI10</t>
+  </si>
+  <si>
+    <t>PI11</t>
+  </si>
+  <si>
+    <t>240MHZ/(79+1)*(59999)=50HZ</t>
+  </si>
+  <si>
+    <t>OCTOSPIM</t>
+  </si>
+  <si>
+    <t>P1_IO3</t>
+  </si>
+  <si>
+    <t>FLASH</t>
+  </si>
+  <si>
+    <t>P1_IO2</t>
+  </si>
+  <si>
+    <t>DCMI</t>
+  </si>
+  <si>
+    <t>HSYNC</t>
+  </si>
+  <si>
+    <t>摄像头</t>
+  </si>
+  <si>
+    <t>LCD</t>
+  </si>
+  <si>
+    <t>PIXCLK</t>
+  </si>
+  <si>
+    <t>CH1N</t>
+  </si>
+  <si>
+    <t>WS2812</t>
+  </si>
+  <si>
+    <t>240MHZ/(0+1)*(299+1)=800KHZ</t>
+  </si>
+  <si>
+    <t>MCO_1</t>
+  </si>
+  <si>
+    <t>USB_OTG_HS</t>
+  </si>
+  <si>
+    <t>DM</t>
+  </si>
+  <si>
+    <t>DP</t>
+  </si>
+  <si>
+    <t>P1_IO1</t>
+  </si>
+  <si>
     <t>BMI088</t>
   </si>
   <si>
-    <t>CS1_Accel</t>
-  </si>
-  <si>
-    <t>PA05</t>
-  </si>
-  <si>
-    <t>PA06</t>
-  </si>
-  <si>
-    <t>TIM3</t>
-  </si>
-  <si>
-    <t>CH1</t>
-  </si>
-  <si>
-    <t>DCMI</t>
+    <t>P1_CLK</t>
+  </si>
+  <si>
+    <t>SPI1</t>
+  </si>
+  <si>
+    <t>VSYNC</t>
+  </si>
+  <si>
+    <t>IIC2</t>
+  </si>
+  <si>
+    <t>REST</t>
+  </si>
+  <si>
+    <t>SPI2</t>
+  </si>
+  <si>
+    <t>?</t>
+  </si>
+  <si>
+    <t>DE</t>
+  </si>
+  <si>
+    <t>RS485-2</t>
+  </si>
+  <si>
+    <t>240MHZ/(0+1)*(59999)=4KHZ</t>
+  </si>
+  <si>
+    <t>IN4</t>
+  </si>
+  <si>
+    <t>PWDN</t>
+  </si>
+  <si>
+    <t>D1</t>
+  </si>
+  <si>
+    <t>SPI3与sbus冲突</t>
+  </si>
+  <si>
+    <t>5V_EN</t>
+  </si>
+  <si>
+    <t>UART5</t>
+  </si>
+  <si>
+    <t>DBUS</t>
+  </si>
+  <si>
+    <t>100000Mbps</t>
+  </si>
+  <si>
+    <t>D5</t>
+  </si>
+  <si>
+    <t>RS485-1</t>
+  </si>
+  <si>
+    <t>P1_IO0</t>
+  </si>
+  <si>
+    <t>CAN3</t>
+  </si>
+  <si>
+    <t>UART9</t>
+  </si>
+  <si>
+    <t>USART10</t>
+  </si>
+  <si>
+    <t>UART10</t>
+  </si>
+  <si>
+    <t>D4</t>
+  </si>
+  <si>
+    <t>D6</t>
+  </si>
+  <si>
+    <t>D7</t>
+  </si>
+  <si>
+    <t>P1_NCS</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>CS</t>
   </si>
   <si>
     <t>PCLK_OUT</t>
   </si>
   <si>
-    <t>PA07</t>
+    <t>I2C1</t>
+  </si>
+  <si>
+    <t>5V接口</t>
+  </si>
+  <si>
+    <t>TIM10</t>
+  </si>
+  <si>
+    <t>HREF</t>
+  </si>
+  <si>
+    <t>MPU6500</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>SPI1</t>
-  </si>
-  <si>
-    <t>MOSI</t>
-  </si>
-  <si>
-    <t>PA08</t>
-  </si>
-  <si>
-    <t>I2C3</t>
-  </si>
-  <si>
-    <t>SCL</t>
-  </si>
-  <si>
-    <t>IST8310</t>
-  </si>
-  <si>
-    <t>磁力计</t>
-  </si>
-  <si>
-    <t>PA09</t>
-  </si>
-  <si>
-    <t>USART1</t>
-  </si>
-  <si>
-    <t>TX</t>
-  </si>
-  <si>
-    <t>UART1</t>
-  </si>
-  <si>
-    <t>4-pin接口</t>
-  </si>
-  <si>
-    <t>PA10</t>
-  </si>
-  <si>
-    <t>I/O</t>
-  </si>
-  <si>
-    <t>USB</t>
-  </si>
-  <si>
-    <t>USB_OTG</t>
-  </si>
-  <si>
-    <t>PA11</t>
-  </si>
-  <si>
-    <t>DM</t>
-  </si>
-  <si>
-    <t>PA12</t>
-  </si>
-  <si>
-    <t>DP</t>
-  </si>
-  <si>
-    <t>PA13</t>
-  </si>
-  <si>
-    <t>SW</t>
-  </si>
-  <si>
-    <t>DIO</t>
-  </si>
-  <si>
-    <t>DEBUG</t>
-  </si>
-  <si>
-    <t>SWDIO</t>
-  </si>
-  <si>
-    <t>PA14</t>
-  </si>
-  <si>
-    <t>CLK</t>
-  </si>
-  <si>
-    <t>SWCLK</t>
-  </si>
-  <si>
-    <t>PA15</t>
-  </si>
-  <si>
-    <t>PB00</t>
-  </si>
-  <si>
-    <t>CS1_Gyro</t>
-  </si>
-  <si>
-    <t>PB01</t>
-  </si>
-  <si>
-    <t>PB02</t>
-  </si>
-  <si>
-    <t>PB03</t>
-  </si>
-  <si>
-    <t>PB04</t>
-  </si>
-  <si>
-    <t>MISO</t>
-  </si>
-  <si>
-    <t>PB05</t>
-  </si>
-  <si>
-    <t>CAN2</t>
-  </si>
-  <si>
-    <t>RX</t>
-  </si>
-  <si>
-    <t>PB06</t>
-  </si>
-  <si>
-    <t>PB07</t>
-  </si>
-  <si>
-    <t>PB08</t>
-  </si>
-  <si>
-    <t>I2C1</t>
-  </si>
-  <si>
-    <t>摄像头</t>
-  </si>
-  <si>
-    <t>PB09</t>
-  </si>
-  <si>
-    <t>SDA</t>
-  </si>
-  <si>
-    <t>PB10</t>
-  </si>
-  <si>
-    <t>PB11</t>
-  </si>
-  <si>
-    <t>PB12</t>
-  </si>
-  <si>
-    <t>SPI2</t>
-  </si>
-  <si>
-    <t>CS</t>
-  </si>
-  <si>
-    <t>EX</t>
-  </si>
-  <si>
-    <t>可配置IO</t>
-  </si>
-  <si>
-    <t>PB13</t>
-  </si>
-  <si>
-    <t>PB14</t>
-  </si>
-  <si>
-    <t>PB15</t>
-  </si>
-  <si>
-    <t>PC00</t>
-  </si>
-  <si>
-    <t>PC01</t>
-  </si>
-  <si>
-    <t>PC02</t>
-  </si>
-  <si>
-    <t>PC03</t>
-  </si>
-  <si>
-    <t>PC04</t>
-  </si>
-  <si>
-    <t>INT1_Accel</t>
-  </si>
-  <si>
-    <t>PC05</t>
-  </si>
-  <si>
-    <t>INT1_Gyro</t>
-  </si>
-  <si>
-    <t>PC06</t>
-  </si>
-  <si>
-    <t>TIM8</t>
-  </si>
-  <si>
-    <t>PWM</t>
-  </si>
-  <si>
-    <t>PC07</t>
-  </si>
-  <si>
-    <t>D1</t>
-  </si>
-  <si>
-    <t>PC08</t>
-  </si>
-  <si>
-    <t>CH3</t>
-  </si>
-  <si>
-    <t>5V接口</t>
-  </si>
-  <si>
-    <t>激光</t>
-  </si>
-  <si>
-    <t>PC09</t>
-  </si>
-  <si>
-    <t>PC10</t>
-  </si>
-  <si>
-    <t>PC11</t>
-  </si>
-  <si>
-    <t>UART3</t>
-  </si>
-  <si>
-    <t>DBUS</t>
-  </si>
-  <si>
-    <t>遥控器</t>
-  </si>
-  <si>
-    <t>PC12</t>
-  </si>
-  <si>
-    <t>PC13</t>
-  </si>
-  <si>
-    <t>PC14</t>
-  </si>
-  <si>
-    <t>PC15</t>
-  </si>
-  <si>
-    <t>PD00</t>
-  </si>
-  <si>
-    <t>CAN1</t>
-  </si>
-  <si>
-    <t>PD01</t>
-  </si>
-  <si>
-    <t>PD02</t>
-  </si>
-  <si>
-    <t>PD03</t>
-  </si>
-  <si>
-    <t>PD04</t>
-  </si>
-  <si>
-    <t>PD05</t>
-  </si>
-  <si>
-    <t>PD06</t>
-  </si>
-  <si>
-    <t>PD07</t>
-  </si>
-  <si>
-    <t>PD08</t>
-  </si>
-  <si>
-    <t>PD09</t>
-  </si>
-  <si>
-    <t>PD10</t>
-  </si>
-  <si>
-    <t>PD11</t>
-  </si>
-  <si>
-    <t>PD12</t>
-  </si>
-  <si>
-    <t>PD13</t>
-  </si>
-  <si>
-    <t>PD14</t>
-  </si>
-  <si>
-    <t>TIM4</t>
-  </si>
-  <si>
-    <t>蜂鸣器</t>
-  </si>
-  <si>
-    <t>PD15</t>
-  </si>
-  <si>
-    <t>PE00</t>
-  </si>
-  <si>
-    <t>D2</t>
-  </si>
-  <si>
-    <t>PE01</t>
-  </si>
-  <si>
-    <t>D3</t>
-  </si>
-  <si>
-    <t>PE02</t>
-  </si>
-  <si>
-    <t>PE03</t>
-  </si>
-  <si>
-    <t>PE04</t>
-  </si>
-  <si>
-    <t>D4</t>
-  </si>
-  <si>
-    <t>PE05</t>
-  </si>
-  <si>
-    <t>D6</t>
-  </si>
-  <si>
-    <t>PE06</t>
-  </si>
-  <si>
-    <t>D7</t>
-  </si>
-  <si>
-    <t>PE07</t>
-  </si>
-  <si>
-    <t>PE08</t>
-  </si>
-  <si>
-    <t>PE09</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>TIM1</t>
-  </si>
-  <si>
-    <t>PE10</t>
-  </si>
-  <si>
-    <t>PE11</t>
-  </si>
-  <si>
-    <t>CH2</t>
-  </si>
-  <si>
-    <t>PE12</t>
-  </si>
-  <si>
-    <t>PE13</t>
-  </si>
-  <si>
-    <t>PE14</t>
-  </si>
-  <si>
-    <t>CH4</t>
-  </si>
-  <si>
-    <t>PE15</t>
-  </si>
-  <si>
-    <t>PF00</t>
-  </si>
-  <si>
-    <t>I2C2</t>
-  </si>
-  <si>
-    <t>PF01</t>
-  </si>
-  <si>
-    <t>PF02</t>
-  </si>
-  <si>
-    <t>PF03</t>
-  </si>
-  <si>
-    <t>PF04</t>
-  </si>
-  <si>
-    <t>PF05</t>
-  </si>
-  <si>
-    <t>PF06</t>
-  </si>
-  <si>
-    <t>TIM10</t>
-  </si>
-  <si>
-    <t>加热</t>
-  </si>
-  <si>
-    <t>PF07</t>
-  </si>
-  <si>
-    <t>PF08</t>
-  </si>
-  <si>
-    <t>PF09</t>
-  </si>
-  <si>
-    <t>PF10</t>
-  </si>
-  <si>
-    <t>ADC1</t>
-  </si>
-  <si>
-    <t>电压检测</t>
-  </si>
-  <si>
-    <t>ADC_BAT</t>
-  </si>
-  <si>
-    <t>PF11</t>
-  </si>
-  <si>
-    <t>PF12</t>
-  </si>
-  <si>
-    <t>PF13</t>
-  </si>
-  <si>
-    <t>PF14</t>
-  </si>
-  <si>
-    <t>PF15</t>
-  </si>
-  <si>
-    <t>PG00</t>
-  </si>
-  <si>
-    <t>PG01</t>
-  </si>
-  <si>
-    <t>PG02</t>
-  </si>
-  <si>
-    <t>PG03</t>
-  </si>
-  <si>
-    <t>DRDY</t>
-  </si>
-  <si>
-    <t>PG04</t>
-  </si>
-  <si>
-    <t>PG05</t>
-  </si>
-  <si>
-    <t>PG06</t>
-  </si>
-  <si>
-    <t>RSTN</t>
-  </si>
-  <si>
-    <t>PG07</t>
-  </si>
-  <si>
-    <t>PG08</t>
-  </si>
-  <si>
-    <t>PG09</t>
-  </si>
-  <si>
-    <t>UART6</t>
-  </si>
-  <si>
-    <t>3-pin接口</t>
-  </si>
-  <si>
-    <t>PG10</t>
-  </si>
-  <si>
-    <t>PG11</t>
-  </si>
-  <si>
-    <t>PG12</t>
-  </si>
-  <si>
-    <t>PG13</t>
-  </si>
-  <si>
-    <t>PG14</t>
-  </si>
-  <si>
-    <t>PG15</t>
-  </si>
-  <si>
-    <t>PH00</t>
-  </si>
-  <si>
-    <t>PH01</t>
-  </si>
-  <si>
-    <t>PH02</t>
-  </si>
-  <si>
-    <t>PH03</t>
-  </si>
-  <si>
-    <t>PH04</t>
-  </si>
-  <si>
-    <t>PH05</t>
-  </si>
-  <si>
-    <t>PH06</t>
-  </si>
-  <si>
-    <t>PH07</t>
-  </si>
-  <si>
-    <t>PH08</t>
-  </si>
-  <si>
-    <t>HREF</t>
-  </si>
-  <si>
-    <t>PH09</t>
-  </si>
-  <si>
-    <t>D0</t>
-  </si>
-  <si>
-    <t>PH10</t>
-  </si>
-  <si>
-    <t>LED</t>
-  </si>
-  <si>
-    <t>LED_B</t>
-  </si>
-  <si>
-    <t>PH11</t>
-  </si>
-  <si>
-    <t>TIM5</t>
-  </si>
-  <si>
-    <t>LED_G</t>
-  </si>
-  <si>
-    <t>PH12</t>
-  </si>
-  <si>
-    <t>LED_R</t>
-  </si>
-  <si>
-    <t>PH13</t>
-  </si>
-  <si>
-    <t>PH14</t>
-  </si>
-  <si>
-    <t>PH15</t>
-  </si>
-  <si>
-    <t>PI00</t>
-  </si>
-  <si>
-    <t>PI01</t>
-  </si>
-  <si>
-    <t>PI02</t>
-  </si>
-  <si>
-    <t>PI03</t>
-  </si>
-  <si>
-    <t>PI04</t>
-  </si>
-  <si>
-    <t>D5</t>
-  </si>
-  <si>
-    <t>PI05</t>
-  </si>
-  <si>
-    <t>VSYNC</t>
-  </si>
-  <si>
-    <t>PI06</t>
-  </si>
-  <si>
-    <t>PI07</t>
-  </si>
-  <si>
-    <t>PI08</t>
-  </si>
-  <si>
-    <t>PI09</t>
-  </si>
-  <si>
-    <t>PI10</t>
-  </si>
-  <si>
-    <t>PI11</t>
-  </si>
-  <si>
-    <t>TIM2</t>
-  </si>
-  <si>
-    <t>OCTOSPIM</t>
-  </si>
-  <si>
-    <t>P1_IO3</t>
-  </si>
-  <si>
-    <t>FLASH</t>
-  </si>
-  <si>
-    <t>P1_IO2</t>
-  </si>
-  <si>
-    <t>HSYNC</t>
-  </si>
-  <si>
-    <t>LCD</t>
-  </si>
-  <si>
-    <t>EXTI</t>
-  </si>
-  <si>
-    <t>PIXCLK</t>
-  </si>
-  <si>
-    <t>CH1N</t>
-  </si>
-  <si>
-    <t>WS2812</t>
-  </si>
-  <si>
-    <t>RCC</t>
-  </si>
-  <si>
-    <t>MCO_1</t>
-  </si>
-  <si>
-    <t>USB_OTG_HS</t>
-  </si>
-  <si>
-    <t>P1_IO1</t>
-  </si>
-  <si>
-    <t>P1_CLK</t>
-  </si>
-  <si>
-    <t>IIC2</t>
-  </si>
-  <si>
-    <t>SCK</t>
-  </si>
-  <si>
-    <t>REST</t>
-  </si>
-  <si>
-    <t>?</t>
-  </si>
-  <si>
-    <t>USART3</t>
-  </si>
-  <si>
-    <t>DE</t>
-  </si>
-  <si>
-    <t>RS485-2</t>
-  </si>
-  <si>
-    <t>TIM12</t>
-  </si>
-  <si>
-    <t>CS1</t>
-  </si>
-  <si>
-    <t>CS2</t>
-  </si>
-  <si>
-    <t>IN4</t>
-  </si>
-  <si>
-    <t>24V电压</t>
-  </si>
-  <si>
-    <t>PWDN</t>
-  </si>
-  <si>
-    <t>SPI3与sbus冲突</t>
-  </si>
-  <si>
-    <t>24V_OUT2</t>
-  </si>
-  <si>
-    <t>POWER</t>
-  </si>
-  <si>
-    <t>24V_OUT1</t>
-  </si>
-  <si>
-    <t>5V_EN</t>
-  </si>
-  <si>
-    <t>UART5</t>
-  </si>
-  <si>
-    <t>100000Mbps</t>
-  </si>
-  <si>
-    <t>USART2</t>
-  </si>
-  <si>
-    <t>RS485-1</t>
-  </si>
-  <si>
-    <t>P1_IO0</t>
-  </si>
-  <si>
-    <t>CAN3</t>
-  </si>
-  <si>
-    <t>UART9</t>
-  </si>
-  <si>
-    <t>UART8</t>
-  </si>
-  <si>
-    <t>USART10</t>
-  </si>
-  <si>
-    <t>UART10</t>
-  </si>
-  <si>
-    <t>UART7</t>
-  </si>
-  <si>
-    <t>INT1</t>
-  </si>
-  <si>
-    <t>P1_NCS</t>
-  </si>
-  <si>
-    <t>INT3</t>
-  </si>
-  <si>
-    <t>RCC</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TIM5</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -870,55 +916,122 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>USB</t>
+    <t>SCK</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>OTG_FS_ID</t>
+    <t>接口</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>OTG_FS_DM</t>
+    <t>接口细节</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>OTG_FS_DP</t>
+    <t>24V_EN2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>ADC3</t>
+    <t>24V_EN1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>IN8</t>
+    <t>摄像头</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>84MHZ/(0+1)*(20999+1)=4KHZ</t>
+    <t>CS_Accel</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>168MHZ/(55+1)*(59999)=50HZ</t>
+    <t>CS_Gyro</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>240MHZ/(79+1)*(59999)=50HZ</t>
+    <t>INT1_Accel</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>240MHZ/(0+1)*(299+1)=800KHZ</t>
+    <t>INT3_Gyro</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>240MHZ/(0+1)*(59999)=4KHZ</t>
+    <t>有的使用PWM</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>IST8310</t>
+    <t>24V输入</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
+    <t>ADC</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>EX</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5V接口</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不知道干什么的，就当悬空了</t>
+  </si>
+  <si>
+    <t>OLED</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KEY</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3Pin排针</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>EX</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DBUS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SDIO</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>D1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SD卡</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>EXTI</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>可调5V电压采集</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>硬件版本控制</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4Pin排针</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PWM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DAC_EXTI</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1307,8 +1420,10 @@
   <dimension ref="A1:G81"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="3" width="21.83203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="14.5" style="1" customWidth="1"/>
+    <col min="3" max="3" width="13.1640625" style="1" customWidth="1"/>
     <col min="4" max="4" width="11.9140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="11.08203125" customWidth="1"/>
     <col min="6" max="6" width="27.6640625" style="1" customWidth="1"/>
     <col min="7" max="7" width="18.5" style="1" customWidth="1"/>
   </cols>
@@ -1324,44 +1439,47 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
+        <v>295</v>
+      </c>
+      <c r="E1" t="s">
+        <v>296</v>
+      </c>
+      <c r="F1" t="s">
         <v>3</v>
-      </c>
-      <c r="F1" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" t="s">
-        <v>229</v>
-      </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="D2" t="s">
-        <v>90</v>
+        <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>288</v>
-      </c>
-      <c r="G2" s="1">
+        <v>234</v>
+      </c>
+      <c r="G2">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="C3" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="D3" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -1369,352 +1487,355 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>229</v>
+        <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>94</v>
+        <v>12</v>
       </c>
       <c r="D4" t="s">
-        <v>90</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>288</v>
-      </c>
-      <c r="G4" s="1">
+        <v>234</v>
+      </c>
+      <c r="G4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="C5" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="D5" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>239</v>
       </c>
       <c r="C6" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="D6" t="s">
-        <v>67</v>
+        <v>241</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="C7" t="s">
-        <v>37</v>
+        <v>77</v>
       </c>
       <c r="D7" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="F7" t="s">
-        <v>236</v>
-      </c>
-      <c r="G7" s="1">
+        <v>231</v>
+      </c>
+      <c r="G7">
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B8" t="s">
-        <v>21</v>
+        <v>239</v>
       </c>
       <c r="C8" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="D8" t="s">
-        <v>67</v>
+        <v>241</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B9" t="s">
-        <v>89</v>
+        <v>223</v>
       </c>
       <c r="C9" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="D9" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="F9" t="s">
-        <v>289</v>
-      </c>
-      <c r="G9" s="1">
+        <v>246</v>
+      </c>
+      <c r="G9">
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B10" t="s">
-        <v>240</v>
+        <v>198</v>
       </c>
       <c r="C10" t="s">
+        <v>247</v>
+      </c>
+      <c r="D10" t="s">
         <v>241</v>
       </c>
-      <c r="D10" t="s">
-        <v>67</v>
+      <c r="E10" t="s">
+        <v>304</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B11" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="C11" t="s">
-        <v>33</v>
+        <v>75</v>
       </c>
       <c r="D11" t="s">
-        <v>34</v>
+        <v>64</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B12" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="C12" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D12" t="s">
-        <v>34</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B13" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="C13" t="s">
-        <v>41</v>
+        <v>249</v>
       </c>
       <c r="D13" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B14" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="C14" t="s">
-        <v>43</v>
+        <v>250</v>
       </c>
       <c r="D14" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15" t="s">
+        <v>43</v>
+      </c>
+      <c r="C15" t="s">
         <v>44</v>
       </c>
-      <c r="B15" t="s">
+      <c r="D15" t="s">
         <v>45</v>
       </c>
-      <c r="C15" t="s">
-        <v>46</v>
-      </c>
-      <c r="D15" t="s">
-        <v>47</v>
-      </c>
-      <c r="G15" s="1">
+      <c r="G15">
         <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B16" t="s">
+        <v>43</v>
+      </c>
+      <c r="C16" t="s">
+        <v>47</v>
+      </c>
+      <c r="D16" t="s">
         <v>45</v>
       </c>
-      <c r="C16" t="s">
-        <v>50</v>
-      </c>
-      <c r="D16" t="s">
-        <v>47</v>
-      </c>
-      <c r="G16" s="1">
+      <c r="G16">
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B17" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="C17" t="s">
-        <v>37</v>
+        <v>77</v>
       </c>
       <c r="D17" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="E17" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="F17" t="s">
-        <v>236</v>
-      </c>
-      <c r="G17" s="1">
+        <v>231</v>
+      </c>
+      <c r="G17">
         <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B18" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="C18" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="D18" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B19" t="s">
-        <v>19</v>
+        <v>58</v>
       </c>
       <c r="C19" t="s">
-        <v>148</v>
+        <v>14</v>
       </c>
       <c r="D19" t="s">
-        <v>15</v>
+        <v>252</v>
       </c>
       <c r="E19" t="s">
-        <v>159</v>
+        <v>59</v>
       </c>
       <c r="F19" t="s">
-        <v>288</v>
-      </c>
-      <c r="G19" s="1">
+        <v>234</v>
+      </c>
+      <c r="G19">
         <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B20" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="C20" t="s">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c r="D20" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B21" t="s">
-        <v>24</v>
+        <v>254</v>
       </c>
       <c r="C21" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D21" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B22" t="s">
-        <v>24</v>
+        <v>254</v>
       </c>
       <c r="C22" t="s">
-        <v>59</v>
+        <v>142</v>
       </c>
       <c r="D22" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B23" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="C23" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D23" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B24" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="C24" t="s">
-        <v>33</v>
+        <v>75</v>
       </c>
       <c r="D24" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B25" t="s">
-        <v>21</v>
+        <v>239</v>
       </c>
       <c r="C25" t="s">
-        <v>222</v>
+        <v>255</v>
       </c>
       <c r="D25" t="s">
-        <v>67</v>
+        <v>241</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
@@ -1722,41 +1843,41 @@
         <v>65</v>
       </c>
       <c r="B26" t="s">
-        <v>21</v>
+        <v>239</v>
       </c>
       <c r="C26" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D26" t="s">
-        <v>67</v>
+        <v>241</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B27" t="s">
-        <v>21</v>
+        <v>239</v>
       </c>
       <c r="C27" t="s">
-        <v>69</v>
+        <v>98</v>
       </c>
       <c r="D27" t="s">
-        <v>67</v>
+        <v>241</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B28" t="s">
-        <v>245</v>
+        <v>256</v>
       </c>
       <c r="C28" t="s">
-        <v>246</v>
+        <v>153</v>
       </c>
       <c r="D28" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
@@ -1764,13 +1885,13 @@
         <v>71</v>
       </c>
       <c r="B29" t="s">
-        <v>245</v>
+        <v>256</v>
       </c>
       <c r="C29" t="s">
-        <v>69</v>
+        <v>98</v>
       </c>
       <c r="D29" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
@@ -1778,89 +1899,89 @@
         <v>72</v>
       </c>
       <c r="B30" t="s">
-        <v>21</v>
+        <v>239</v>
       </c>
       <c r="C30" t="s">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="D30" t="s">
-        <v>67</v>
+        <v>241</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B31" t="s">
-        <v>73</v>
+        <v>258</v>
       </c>
       <c r="C31" t="s">
-        <v>246</v>
+        <v>153</v>
       </c>
       <c r="D31" t="s">
-        <v>15</v>
+        <v>252</v>
       </c>
       <c r="F31" t="s">
-        <v>248</v>
-      </c>
-      <c r="G31" s="1">
+        <v>259</v>
+      </c>
+      <c r="G31">
         <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B32" t="s">
-        <v>249</v>
+        <v>121</v>
       </c>
       <c r="C32" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="D32" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B33" t="s">
-        <v>252</v>
+        <v>206</v>
       </c>
       <c r="C33" t="s">
-        <v>144</v>
+        <v>10</v>
       </c>
       <c r="D33" t="s">
-        <v>124</v>
+        <v>207</v>
       </c>
       <c r="F33" t="s">
-        <v>290</v>
-      </c>
-      <c r="G33" s="1">
+        <v>262</v>
+      </c>
+      <c r="G33">
         <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B34" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="C34" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="D34" t="s">
-        <v>15</v>
+        <v>252</v>
       </c>
       <c r="E34" t="s">
-        <v>253</v>
+        <v>300</v>
       </c>
       <c r="F34" t="s">
-        <v>14</v>
-      </c>
-      <c r="G34" s="1">
+        <v>26</v>
+      </c>
+      <c r="G34">
         <v>1</v>
       </c>
     </row>
@@ -1869,121 +1990,120 @@
         <v>81</v>
       </c>
       <c r="B35" t="s">
-        <v>73</v>
+        <v>258</v>
       </c>
       <c r="C35" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D35" t="s">
-        <v>15</v>
-      </c>
-      <c r="F35" t="s">
-        <v>248</v>
-      </c>
-      <c r="G35" s="1">
+        <v>252</v>
+      </c>
+      <c r="F35"/>
+      <c r="G35">
         <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B36" t="s">
-        <v>73</v>
+        <v>258</v>
       </c>
       <c r="C36" t="s">
-        <v>59</v>
+        <v>142</v>
       </c>
       <c r="D36" t="s">
-        <v>15</v>
-      </c>
-      <c r="F36" t="s">
-        <v>248</v>
-      </c>
-      <c r="G36" s="1">
+        <v>252</v>
+      </c>
+      <c r="F36"/>
+      <c r="G36">
         <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B37" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="C37" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="D37" t="s">
-        <v>15</v>
+        <v>252</v>
       </c>
       <c r="E37" t="s">
-        <v>254</v>
+        <v>301</v>
       </c>
       <c r="F37" t="s">
-        <v>14</v>
-      </c>
-      <c r="G37" s="1">
+        <v>26</v>
+      </c>
+      <c r="G37">
         <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B38" t="s">
-        <v>164</v>
+        <v>50</v>
       </c>
       <c r="C38" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="D38" t="s">
-        <v>256</v>
-      </c>
-      <c r="G38" s="1">
+        <v>305</v>
+      </c>
+      <c r="E38" t="s">
+        <v>171</v>
+      </c>
+      <c r="G38">
         <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B39" t="s">
-        <v>21</v>
+        <v>239</v>
       </c>
       <c r="C39" t="s">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="D39" t="s">
-        <v>67</v>
+        <v>241</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B40" t="s">
-        <v>21</v>
+        <v>239</v>
       </c>
       <c r="C40" t="s">
-        <v>203</v>
+        <v>95</v>
       </c>
       <c r="D40" t="s">
-        <v>67</v>
+        <v>241</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B41" t="s">
-        <v>21</v>
+        <v>239</v>
       </c>
       <c r="C41" t="s">
-        <v>92</v>
+        <v>265</v>
       </c>
       <c r="D41" t="s">
-        <v>67</v>
+        <v>241</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
@@ -1991,13 +2111,13 @@
         <v>93</v>
       </c>
       <c r="B42" t="s">
-        <v>21</v>
+        <v>239</v>
       </c>
       <c r="C42" t="s">
-        <v>127</v>
+        <v>100</v>
       </c>
       <c r="D42" t="s">
-        <v>67</v>
+        <v>241</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
@@ -2005,41 +2125,41 @@
         <v>97</v>
       </c>
       <c r="B43" t="s">
-        <v>21</v>
+        <v>239</v>
       </c>
       <c r="C43" t="s">
-        <v>129</v>
+        <v>102</v>
       </c>
       <c r="D43" t="s">
-        <v>67</v>
+        <v>241</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B44" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="C44" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D44" t="s">
-        <v>75</v>
+        <v>18</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B45" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="C45" t="s">
-        <v>59</v>
+        <v>142</v>
       </c>
       <c r="D45" t="s">
-        <v>75</v>
+        <v>18</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
@@ -2047,613 +2167,615 @@
         <v>103</v>
       </c>
       <c r="B46" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="C46" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D46" t="s">
-        <v>75</v>
+        <v>18</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B47" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="C47" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="D47" t="s">
-        <v>259</v>
+        <v>297</v>
       </c>
       <c r="E47" t="s">
-        <v>260</v>
+        <v>201</v>
       </c>
       <c r="F47" t="s">
-        <v>14</v>
-      </c>
-      <c r="G47" s="1">
+        <v>26</v>
+      </c>
+      <c r="G47">
         <v>1</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B48" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="C48" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="D48" t="s">
-        <v>261</v>
+        <v>298</v>
       </c>
       <c r="E48" t="s">
-        <v>260</v>
+        <v>201</v>
       </c>
       <c r="F48" t="s">
-        <v>14</v>
-      </c>
-      <c r="G48" s="1">
+        <v>26</v>
+      </c>
+      <c r="G48">
         <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B49" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="C49" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="D49" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="E49" t="s">
-        <v>260</v>
+        <v>201</v>
       </c>
       <c r="F49" t="s">
-        <v>14</v>
-      </c>
-      <c r="G49" s="1">
+        <v>26</v>
+      </c>
+      <c r="G49">
         <v>1</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B50" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C50" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D50" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
+        <v>110</v>
+      </c>
+      <c r="B51" t="s">
         <v>109</v>
       </c>
-      <c r="B51" t="s">
-        <v>108</v>
-      </c>
       <c r="C51" t="s">
-        <v>33</v>
+        <v>75</v>
       </c>
       <c r="D51" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B52" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="C52" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D52" t="s">
-        <v>101</v>
+        <v>269</v>
       </c>
       <c r="F52" t="s">
-        <v>264</v>
-      </c>
-      <c r="G52" s="1">
+        <v>270</v>
+      </c>
+      <c r="G52">
         <v>1</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B53" t="s">
-        <v>21</v>
+        <v>239</v>
       </c>
       <c r="C53" t="s">
-        <v>220</v>
+        <v>271</v>
       </c>
       <c r="D53" t="s">
-        <v>67</v>
+        <v>241</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B54" t="s">
-        <v>265</v>
+        <v>116</v>
       </c>
       <c r="C54" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="D54" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B55" t="s">
-        <v>265</v>
+        <v>116</v>
       </c>
       <c r="C55" t="s">
-        <v>33</v>
+        <v>75</v>
       </c>
       <c r="D55" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B56" t="s">
-        <v>265</v>
+        <v>116</v>
       </c>
       <c r="C56" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D56" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="B57" t="s">
-        <v>24</v>
+        <v>254</v>
       </c>
       <c r="C57" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D57" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="B58" t="s">
-        <v>249</v>
+        <v>121</v>
       </c>
       <c r="C58" t="s">
-        <v>33</v>
+        <v>75</v>
       </c>
       <c r="D58" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="B59" t="s">
-        <v>249</v>
+        <v>121</v>
       </c>
       <c r="C59" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D59" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="B60" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="C60" t="s">
-        <v>37</v>
+        <v>77</v>
       </c>
       <c r="D60" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="E60" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="F60" t="s">
-        <v>236</v>
-      </c>
-      <c r="G60" s="1">
+        <v>231</v>
+      </c>
+      <c r="G60">
         <v>1</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B61" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="C61" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="D61" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="B62" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="C62" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D62" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="B63" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="C63" t="s">
-        <v>33</v>
+        <v>75</v>
       </c>
       <c r="D63" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="B64" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="C64" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D64" t="s">
-        <v>75</v>
+        <v>18</v>
       </c>
       <c r="E64" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="B65" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="C65" t="s">
-        <v>33</v>
+        <v>75</v>
       </c>
       <c r="D65" t="s">
-        <v>75</v>
+        <v>18</v>
       </c>
       <c r="E65" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="B66" t="s">
-        <v>270</v>
+        <v>132</v>
       </c>
       <c r="C66" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D66" t="s">
-        <v>75</v>
+        <v>18</v>
       </c>
       <c r="E66" t="s">
-        <v>270</v>
+        <v>132</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="B67" t="s">
-        <v>270</v>
+        <v>132</v>
       </c>
       <c r="C67" t="s">
-        <v>33</v>
+        <v>75</v>
       </c>
       <c r="D67" t="s">
-        <v>75</v>
+        <v>18</v>
       </c>
       <c r="E67" t="s">
-        <v>270</v>
+        <v>132</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="B68" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="C68" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D68" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="B69" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="C69" t="s">
-        <v>33</v>
+        <v>75</v>
       </c>
       <c r="D69" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="B70" t="s">
-        <v>21</v>
+        <v>239</v>
       </c>
       <c r="C70" t="s">
-        <v>133</v>
+        <v>278</v>
       </c>
       <c r="D70" t="s">
-        <v>67</v>
+        <v>241</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="B71" t="s">
-        <v>21</v>
+        <v>239</v>
       </c>
       <c r="C71" t="s">
-        <v>135</v>
+        <v>279</v>
       </c>
       <c r="D71" t="s">
-        <v>67</v>
+        <v>241</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="B72" t="s">
-        <v>21</v>
+        <v>239</v>
       </c>
       <c r="C72" t="s">
-        <v>137</v>
+        <v>280</v>
       </c>
       <c r="D72" t="s">
-        <v>67</v>
+        <v>241</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="B73" t="s">
-        <v>273</v>
+        <v>145</v>
       </c>
       <c r="C73" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D73" t="s">
-        <v>273</v>
+        <v>145</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="B74" t="s">
-        <v>273</v>
+        <v>145</v>
       </c>
       <c r="C74" t="s">
-        <v>33</v>
+        <v>75</v>
       </c>
       <c r="D74" t="s">
-        <v>273</v>
+        <v>145</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="B75" t="s">
-        <v>141</v>
+        <v>34</v>
       </c>
       <c r="C75" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="D75" t="s">
-        <v>90</v>
+        <v>7</v>
       </c>
       <c r="F75" t="s">
-        <v>288</v>
-      </c>
-      <c r="G75" s="1">
+        <v>234</v>
+      </c>
+      <c r="G75">
         <v>1</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="B76" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="C76" t="s">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="D76" t="s">
-        <v>15</v>
+        <v>252</v>
       </c>
       <c r="E76" t="s">
-        <v>274</v>
+        <v>302</v>
       </c>
       <c r="F76" t="s">
-        <v>7</v>
-      </c>
-      <c r="G76" s="1">
+        <v>23</v>
+      </c>
+      <c r="G76">
         <v>1</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="B77" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="C77" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="D77" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="B78" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="C78" t="s">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="D78" t="s">
-        <v>15</v>
+        <v>252</v>
       </c>
       <c r="E78" t="s">
-        <v>276</v>
+        <v>303</v>
       </c>
       <c r="F78" t="s">
-        <v>7</v>
-      </c>
-      <c r="G78" s="1">
+        <v>23</v>
+      </c>
+      <c r="G78">
         <v>1</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="B79" t="s">
-        <v>292</v>
+        <v>282</v>
       </c>
       <c r="C79" t="s">
-        <v>94</v>
+        <v>12</v>
       </c>
       <c r="D79" t="s">
-        <v>90</v>
+        <v>7</v>
       </c>
       <c r="F79" t="s">
-        <v>288</v>
-      </c>
-      <c r="G79" s="1">
+        <v>234</v>
+      </c>
+      <c r="G79">
         <v>1</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="B80" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="C80" t="s">
-        <v>37</v>
+        <v>77</v>
       </c>
       <c r="D80" t="s">
-        <v>75</v>
+        <v>18</v>
       </c>
       <c r="E80" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="F80" t="s">
-        <v>236</v>
-      </c>
-      <c r="G80" s="1">
+        <v>231</v>
+      </c>
+      <c r="G80">
         <v>1</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="B81" t="s">
-        <v>24</v>
+        <v>254</v>
       </c>
       <c r="C81" t="s">
-        <v>74</v>
+        <v>283</v>
       </c>
       <c r="D81" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:G81" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G141"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:J141"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="12.58203125" customWidth="1"/>
-    <col min="3" max="3" width="14.1640625" customWidth="1"/>
+    <col min="2" max="2" width="12.58203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="14.1640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="11.33203125" customWidth="1"/>
     <col min="6" max="6" width="28.9140625" style="1" customWidth="1"/>
-    <col min="10" max="10" width="27.83203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="27.83203125" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
@@ -2667,30 +2789,30 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
+        <v>295</v>
+      </c>
+      <c r="E1" t="s">
+        <v>296</v>
+      </c>
+      <c r="F1" t="s">
         <v>3</v>
-      </c>
-      <c r="F1" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="D2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="F2" t="s">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -2698,7 +2820,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -2708,27 +2830,27 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="D6" t="s">
-        <v>15</v>
+        <v>252</v>
       </c>
       <c r="E6" t="s">
-        <v>16</v>
+        <v>300</v>
       </c>
       <c r="F6" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="G6">
         <v>1</v>
@@ -2736,39 +2858,39 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
+        <v>58</v>
       </c>
       <c r="C8" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="D8" t="s">
-        <v>21</v>
+        <v>299</v>
       </c>
       <c r="E8" t="s">
-        <v>22</v>
+        <v>284</v>
       </c>
       <c r="F8"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B9" t="s">
-        <v>24</v>
+        <v>254</v>
       </c>
       <c r="C9" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D9" t="s">
-        <v>15</v>
+        <v>252</v>
       </c>
       <c r="F9"/>
       <c r="G9">
@@ -2777,19 +2899,16 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B10" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D10" t="s">
-        <v>291</v>
-      </c>
-      <c r="E10" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F10"/>
       <c r="G10">
@@ -2798,85 +2917,76 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B11" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="C11" t="s">
-        <v>33</v>
+        <v>75</v>
       </c>
       <c r="D11" t="s">
-        <v>34</v>
-      </c>
-      <c r="E11" t="s">
-        <v>35</v>
+        <v>64</v>
       </c>
       <c r="F11"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
+        <v>35</v>
+      </c>
+      <c r="B12" t="s">
         <v>36</v>
       </c>
-      <c r="B12" t="s">
-        <v>280</v>
-      </c>
       <c r="C12" t="s">
-        <v>281</v>
+        <v>37</v>
       </c>
       <c r="D12" t="s">
-        <v>38</v>
-      </c>
-      <c r="E12" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F12"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B13" t="s">
-        <v>280</v>
+        <v>36</v>
       </c>
       <c r="C13" t="s">
-        <v>282</v>
+        <v>39</v>
       </c>
       <c r="D13" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F13"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B14" t="s">
-        <v>280</v>
+        <v>36</v>
       </c>
       <c r="C14" t="s">
-        <v>283</v>
+        <v>41</v>
       </c>
       <c r="D14" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F14"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15" t="s">
+        <v>43</v>
+      </c>
+      <c r="C15" t="s">
         <v>44</v>
       </c>
-      <c r="B15" t="s">
+      <c r="D15" t="s">
         <v>45</v>
-      </c>
-      <c r="C15" t="s">
-        <v>46</v>
-      </c>
-      <c r="D15" t="s">
-        <v>47</v>
-      </c>
-      <c r="E15" t="s">
-        <v>48</v>
       </c>
       <c r="F15"/>
       <c r="G15">
@@ -2885,19 +2995,16 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B16" t="s">
+        <v>43</v>
+      </c>
+      <c r="C16" t="s">
+        <v>47</v>
+      </c>
+      <c r="D16" t="s">
         <v>45</v>
-      </c>
-      <c r="C16" t="s">
-        <v>50</v>
-      </c>
-      <c r="D16" t="s">
-        <v>47</v>
-      </c>
-      <c r="E16" t="s">
-        <v>51</v>
       </c>
       <c r="F16"/>
       <c r="G16">
@@ -2906,27 +3013,27 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B18" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="C18" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="D18" t="s">
-        <v>15</v>
+        <v>252</v>
       </c>
       <c r="E18" t="s">
-        <v>54</v>
+        <v>301</v>
       </c>
       <c r="F18" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="G18">
         <v>1</v>
@@ -2934,26 +3041,26 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B21" t="s">
-        <v>24</v>
+        <v>254</v>
       </c>
       <c r="C21" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D21" t="s">
-        <v>15</v>
+        <v>252</v>
       </c>
       <c r="F21"/>
       <c r="G21">
@@ -2962,16 +3069,16 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B22" t="s">
-        <v>24</v>
+        <v>254</v>
       </c>
       <c r="C22" t="s">
-        <v>59</v>
+        <v>142</v>
       </c>
       <c r="D22" t="s">
-        <v>15</v>
+        <v>252</v>
       </c>
       <c r="F22"/>
       <c r="G22">
@@ -2980,49 +3087,46 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B23" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="C23" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D23" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="F23"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B24" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="C24" t="s">
-        <v>33</v>
+        <v>75</v>
       </c>
       <c r="D24" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="F24"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
+        <v>61</v>
+      </c>
+      <c r="B25" t="s">
+        <v>62</v>
+      </c>
+      <c r="C25" t="s">
+        <v>63</v>
+      </c>
+      <c r="D25" t="s">
         <v>64</v>
-      </c>
-      <c r="B25" t="s">
-        <v>32</v>
-      </c>
-      <c r="C25" t="s">
-        <v>62</v>
-      </c>
-      <c r="D25" t="s">
-        <v>34</v>
-      </c>
-      <c r="E25" t="s">
-        <v>35</v>
       </c>
       <c r="F25"/>
     </row>
@@ -3031,40 +3135,40 @@
         <v>65</v>
       </c>
       <c r="B26" t="s">
-        <v>66</v>
+        <v>285</v>
       </c>
       <c r="C26" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D26" t="s">
-        <v>67</v>
+        <v>241</v>
       </c>
       <c r="E26" t="s">
-        <v>21</v>
+        <v>239</v>
       </c>
       <c r="F26"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B27" t="s">
-        <v>66</v>
+        <v>285</v>
       </c>
       <c r="C27" t="s">
-        <v>69</v>
+        <v>98</v>
       </c>
       <c r="D27" t="s">
-        <v>67</v>
+        <v>241</v>
       </c>
       <c r="E27" t="s">
-        <v>21</v>
+        <v>239</v>
       </c>
       <c r="F27"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
@@ -3077,76 +3181,64 @@
         <v>72</v>
       </c>
       <c r="B30" t="s">
-        <v>73</v>
+        <v>258</v>
       </c>
       <c r="C30" t="s">
-        <v>74</v>
+        <v>283</v>
       </c>
       <c r="D30" t="s">
-        <v>75</v>
-      </c>
-      <c r="E30" t="s">
-        <v>76</v>
+        <v>18</v>
       </c>
       <c r="F30"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B31" t="s">
-        <v>73</v>
+        <v>258</v>
       </c>
       <c r="C31" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D31" t="s">
-        <v>75</v>
-      </c>
-      <c r="E31" t="s">
-        <v>76</v>
+        <v>18</v>
       </c>
       <c r="F31"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B32" t="s">
-        <v>73</v>
+        <v>258</v>
       </c>
       <c r="C32" t="s">
-        <v>59</v>
+        <v>142</v>
       </c>
       <c r="D32" t="s">
-        <v>75</v>
-      </c>
-      <c r="E32" t="s">
-        <v>76</v>
+        <v>18</v>
       </c>
       <c r="F32"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B33" t="s">
-        <v>73</v>
+        <v>258</v>
       </c>
       <c r="C33" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D33" t="s">
-        <v>75</v>
-      </c>
-      <c r="E33" t="s">
-        <v>76</v>
+        <v>18</v>
       </c>
       <c r="F33"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
@@ -3156,32 +3248,32 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B38" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="C38" t="s">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="D38" t="s">
-        <v>15</v>
+        <v>252</v>
       </c>
       <c r="E38" t="s">
-        <v>85</v>
+        <v>302</v>
       </c>
       <c r="F38" t="s">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="G38">
         <v>1</v>
@@ -3189,22 +3281,22 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B39" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="C39" t="s">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="D39" t="s">
-        <v>15</v>
+        <v>252</v>
       </c>
       <c r="E39" t="s">
-        <v>87</v>
+        <v>303</v>
       </c>
       <c r="F39" t="s">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="G39">
         <v>1</v>
@@ -3212,19 +3304,19 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B40" t="s">
-        <v>89</v>
+        <v>223</v>
       </c>
       <c r="C40" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="D40" t="s">
-        <v>90</v>
+        <v>7</v>
       </c>
       <c r="F40" t="s">
-        <v>287</v>
+        <v>8</v>
       </c>
       <c r="G40">
         <v>1</v>
@@ -3232,16 +3324,16 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B41" t="s">
-        <v>21</v>
+        <v>239</v>
       </c>
       <c r="C41" t="s">
-        <v>92</v>
+        <v>265</v>
       </c>
       <c r="D41" t="s">
-        <v>67</v>
+        <v>241</v>
       </c>
       <c r="F41"/>
     </row>
@@ -3250,19 +3342,19 @@
         <v>93</v>
       </c>
       <c r="B42" t="s">
-        <v>19</v>
+        <v>58</v>
       </c>
       <c r="C42" t="s">
-        <v>94</v>
+        <v>12</v>
       </c>
       <c r="D42" t="s">
-        <v>95</v>
+        <v>286</v>
       </c>
       <c r="E42" t="s">
-        <v>96</v>
+        <v>194</v>
       </c>
       <c r="F42" t="s">
-        <v>286</v>
+        <v>208</v>
       </c>
       <c r="G42">
         <v>1</v>
@@ -3273,16 +3365,13 @@
         <v>97</v>
       </c>
       <c r="B43" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C43" t="s">
-        <v>69</v>
+        <v>98</v>
       </c>
       <c r="D43" t="s">
-        <v>29</v>
-      </c>
-      <c r="E43" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F43"/>
       <c r="G43">
@@ -3291,24 +3380,21 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B45" t="s">
-        <v>100</v>
+        <v>122</v>
       </c>
       <c r="C45" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D45" t="s">
-        <v>101</v>
-      </c>
-      <c r="E45" t="s">
-        <v>102</v>
+        <v>269</v>
       </c>
       <c r="F45"/>
       <c r="G45">
@@ -3322,124 +3408,124 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B50" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C50" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D50" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F50"/>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
+        <v>110</v>
+      </c>
+      <c r="B51" t="s">
         <v>109</v>
       </c>
-      <c r="B51" t="s">
-        <v>108</v>
-      </c>
       <c r="C51" t="s">
-        <v>33</v>
+        <v>75</v>
       </c>
       <c r="D51" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F51"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="B64" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="C64" t="s">
-        <v>94</v>
+        <v>12</v>
       </c>
       <c r="D64" t="s">
-        <v>124</v>
+        <v>207</v>
       </c>
       <c r="F64" t="s">
-        <v>286</v>
+        <v>208</v>
       </c>
       <c r="G64">
         <v>1</v>
@@ -3447,119 +3533,119 @@
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="B66" t="s">
-        <v>21</v>
+        <v>239</v>
       </c>
       <c r="C66" t="s">
-        <v>127</v>
+        <v>100</v>
       </c>
       <c r="D66" t="s">
-        <v>67</v>
+        <v>241</v>
       </c>
       <c r="F66"/>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="B67" t="s">
-        <v>21</v>
+        <v>239</v>
       </c>
       <c r="C67" t="s">
-        <v>129</v>
+        <v>102</v>
       </c>
       <c r="D67" t="s">
-        <v>67</v>
+        <v>241</v>
       </c>
       <c r="F67"/>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="B70" t="s">
-        <v>21</v>
+        <v>239</v>
       </c>
       <c r="C70" t="s">
-        <v>133</v>
+        <v>278</v>
       </c>
       <c r="D70" t="s">
-        <v>67</v>
+        <v>241</v>
       </c>
       <c r="F70"/>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="B71" t="s">
-        <v>21</v>
+        <v>239</v>
       </c>
       <c r="C71" t="s">
-        <v>135</v>
+        <v>279</v>
       </c>
       <c r="D71" t="s">
-        <v>67</v>
+        <v>241</v>
       </c>
       <c r="F71"/>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="B72" t="s">
-        <v>21</v>
+        <v>239</v>
       </c>
       <c r="C72" t="s">
-        <v>137</v>
+        <v>280</v>
       </c>
       <c r="D72" t="s">
-        <v>67</v>
+        <v>241</v>
       </c>
       <c r="F72"/>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="B75" t="s">
-        <v>141</v>
+        <v>34</v>
       </c>
       <c r="C75" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="D75" t="s">
-        <v>90</v>
+        <v>7</v>
       </c>
       <c r="F75" t="s">
-        <v>287</v>
+        <v>8</v>
       </c>
       <c r="G75">
         <v>1</v>
@@ -3567,24 +3653,24 @@
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="B77" t="s">
-        <v>141</v>
+        <v>34</v>
       </c>
       <c r="C77" t="s">
-        <v>144</v>
+        <v>10</v>
       </c>
       <c r="D77" t="s">
-        <v>90</v>
+        <v>7</v>
       </c>
       <c r="F77" t="s">
-        <v>287</v>
+        <v>8</v>
       </c>
       <c r="G77">
         <v>1</v>
@@ -3592,24 +3678,24 @@
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="B79" t="s">
-        <v>141</v>
+        <v>34</v>
       </c>
       <c r="C79" t="s">
-        <v>94</v>
+        <v>12</v>
       </c>
       <c r="D79" t="s">
-        <v>90</v>
+        <v>7</v>
       </c>
       <c r="F79" t="s">
-        <v>287</v>
+        <v>8</v>
       </c>
       <c r="G79">
         <v>1</v>
@@ -3617,19 +3703,19 @@
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="B80" t="s">
-        <v>141</v>
+        <v>34</v>
       </c>
       <c r="C80" t="s">
-        <v>148</v>
+        <v>14</v>
       </c>
       <c r="D80" t="s">
-        <v>90</v>
+        <v>7</v>
       </c>
       <c r="F80" t="s">
-        <v>287</v>
+        <v>8</v>
       </c>
       <c r="G80">
         <v>1</v>
@@ -3637,83 +3723,77 @@
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="B82" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="C82" t="s">
-        <v>69</v>
+        <v>98</v>
       </c>
       <c r="D82" t="s">
-        <v>75</v>
-      </c>
-      <c r="E82" t="s">
-        <v>76</v>
+        <v>18</v>
       </c>
       <c r="F82"/>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="B83" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="C83" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D83" t="s">
-        <v>75</v>
-      </c>
-      <c r="E83" t="s">
-        <v>76</v>
+        <v>18</v>
       </c>
       <c r="F83"/>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="B88" t="s">
-        <v>158</v>
+        <v>287</v>
       </c>
       <c r="C88" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="D88" t="s">
-        <v>15</v>
+        <v>252</v>
       </c>
       <c r="E88" t="s">
-        <v>159</v>
+        <v>59</v>
       </c>
       <c r="F88" t="s">
-        <v>287</v>
+        <v>8</v>
       </c>
       <c r="G88">
         <v>1</v>
@@ -3721,34 +3801,34 @@
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="B92" t="s">
-        <v>284</v>
+        <v>162</v>
       </c>
       <c r="C92" t="s">
-        <v>285</v>
+        <v>51</v>
       </c>
       <c r="D92" t="s">
-        <v>165</v>
+        <v>305</v>
       </c>
       <c r="E92" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="F92"/>
       <c r="G92">
@@ -3757,62 +3837,62 @@
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="B101" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="C101" t="s">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="D101" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E101" t="s">
-        <v>176</v>
+        <v>137</v>
       </c>
       <c r="F101" t="s">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="G101">
         <v>1</v>
@@ -3820,32 +3900,32 @@
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="B104" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="C104" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="D104" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E104" t="s">
-        <v>180</v>
+        <v>135</v>
       </c>
       <c r="F104" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="G104">
         <v>1</v>
@@ -3853,81 +3933,75 @@
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="B107" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="C107" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D107" t="s">
-        <v>184</v>
-      </c>
-      <c r="E107" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="F107"/>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B112" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="C112" t="s">
-        <v>33</v>
+        <v>75</v>
       </c>
       <c r="D112" t="s">
-        <v>184</v>
-      </c>
-      <c r="E112" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="F112"/>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="B114" t="s">
-        <v>277</v>
+        <v>198</v>
       </c>
       <c r="G114">
         <v>1</v>
@@ -3935,10 +4009,10 @@
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="B115" t="s">
-        <v>277</v>
+        <v>198</v>
       </c>
       <c r="G115">
         <v>1</v>
@@ -3946,82 +4020,79 @@
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>199</v>
+        <v>209</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="B122" t="s">
-        <v>21</v>
+        <v>239</v>
       </c>
       <c r="C122" t="s">
-        <v>201</v>
+        <v>288</v>
       </c>
       <c r="D122" t="s">
-        <v>67</v>
+        <v>241</v>
       </c>
       <c r="F122"/>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="B123" t="s">
-        <v>21</v>
+        <v>239</v>
       </c>
       <c r="C123" t="s">
-        <v>203</v>
+        <v>95</v>
       </c>
       <c r="D123" t="s">
-        <v>67</v>
+        <v>241</v>
       </c>
       <c r="F123"/>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="B124" t="s">
-        <v>278</v>
+        <v>213</v>
       </c>
       <c r="C124" t="s">
-        <v>279</v>
+        <v>6</v>
       </c>
       <c r="D124" t="s">
-        <v>205</v>
-      </c>
-      <c r="E124" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="F124" t="s">
-        <v>286</v>
+        <v>208</v>
       </c>
       <c r="G124">
         <v>1</v>
@@ -4029,22 +4100,19 @@
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="B125" t="s">
+        <v>213</v>
+      </c>
+      <c r="C125" t="s">
+        <v>10</v>
+      </c>
+      <c r="D125" t="s">
+        <v>176</v>
+      </c>
+      <c r="F125" t="s">
         <v>208</v>
-      </c>
-      <c r="C125" t="s">
-        <v>144</v>
-      </c>
-      <c r="D125" t="s">
-        <v>205</v>
-      </c>
-      <c r="E125" t="s">
-        <v>209</v>
-      </c>
-      <c r="F125" t="s">
-        <v>286</v>
       </c>
       <c r="G125">
         <v>1</v>
@@ -4052,22 +4120,19 @@
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="B126" t="s">
+        <v>213</v>
+      </c>
+      <c r="C126" t="s">
+        <v>12</v>
+      </c>
+      <c r="D126" t="s">
+        <v>151</v>
+      </c>
+      <c r="F126" t="s">
         <v>208</v>
-      </c>
-      <c r="C126" t="s">
-        <v>94</v>
-      </c>
-      <c r="D126" t="s">
-        <v>205</v>
-      </c>
-      <c r="E126" t="s">
-        <v>211</v>
-      </c>
-      <c r="F126" t="s">
-        <v>286</v>
       </c>
       <c r="G126">
         <v>1</v>
@@ -4075,84 +4140,84 @@
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="B134" t="s">
-        <v>21</v>
+        <v>239</v>
       </c>
       <c r="C134" t="s">
-        <v>220</v>
+        <v>271</v>
       </c>
       <c r="D134" t="s">
-        <v>67</v>
+        <v>241</v>
       </c>
       <c r="F134"/>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="B135" t="s">
-        <v>21</v>
+        <v>239</v>
       </c>
       <c r="C135" t="s">
-        <v>222</v>
+        <v>255</v>
       </c>
       <c r="D135" t="s">
-        <v>67</v>
+        <v>241</v>
       </c>
       <c r="F135"/>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
+        <v>227</v>
+      </c>
+      <c r="B136" t="s">
         <v>223</v>
       </c>
-      <c r="B136" t="s">
-        <v>89</v>
-      </c>
       <c r="C136" t="s">
-        <v>144</v>
+        <v>10</v>
       </c>
       <c r="D136" t="s">
-        <v>90</v>
+        <v>7</v>
       </c>
       <c r="F136" t="s">
-        <v>287</v>
+        <v>8</v>
       </c>
       <c r="G136">
         <v>1</v>
@@ -4160,19 +4225,19 @@
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="B137" t="s">
-        <v>89</v>
+        <v>223</v>
       </c>
       <c r="C137" t="s">
-        <v>94</v>
+        <v>12</v>
       </c>
       <c r="D137" t="s">
-        <v>90</v>
+        <v>7</v>
       </c>
       <c r="F137" t="s">
-        <v>287</v>
+        <v>8</v>
       </c>
       <c r="G137">
         <v>1</v>
@@ -4180,22 +4245,1685 @@
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
+        <v>233</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="D1:D141" xr:uid="{00000000-0001-0000-0200-000000000000}"/>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:F141"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="3" max="3" width="15.58203125" customWidth="1"/>
+    <col min="4" max="4" width="10.33203125" customWidth="1"/>
+    <col min="5" max="5" width="15.1640625" customWidth="1"/>
+    <col min="6" max="6" width="31" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>295</v>
+      </c>
+      <c r="E1" t="s">
+        <v>296</v>
+      </c>
+      <c r="F1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" t="s">
+        <v>310</v>
+      </c>
+      <c r="E8" t="s">
+        <v>311</v>
+      </c>
+      <c r="F8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" t="s">
+        <v>291</v>
+      </c>
+      <c r="C9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" t="s">
+        <v>27</v>
+      </c>
+      <c r="E9" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10" t="s">
+        <v>292</v>
+      </c>
+      <c r="C10" t="s">
+        <v>293</v>
+      </c>
+      <c r="D10" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>35</v>
+      </c>
+      <c r="B12" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12" t="s">
+        <v>37</v>
+      </c>
+      <c r="D12" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>38</v>
+      </c>
+      <c r="B13" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" t="s">
+        <v>39</v>
+      </c>
+      <c r="D13" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>40</v>
+      </c>
+      <c r="B14" t="s">
+        <v>36</v>
+      </c>
+      <c r="C14" t="s">
+        <v>41</v>
+      </c>
+      <c r="D14" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15" t="s">
+        <v>43</v>
+      </c>
+      <c r="C15" t="s">
+        <v>44</v>
+      </c>
+      <c r="D15" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>46</v>
+      </c>
+      <c r="B16" t="s">
+        <v>43</v>
+      </c>
+      <c r="C16" t="s">
+        <v>47</v>
+      </c>
+      <c r="D16" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>49</v>
+      </c>
+      <c r="B18" t="s">
+        <v>50</v>
+      </c>
+      <c r="C18" t="s">
+        <v>51</v>
+      </c>
+      <c r="D18" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>52</v>
+      </c>
+      <c r="B19" t="s">
+        <v>50</v>
+      </c>
+      <c r="C19" t="s">
+        <v>53</v>
+      </c>
+      <c r="D19" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>54</v>
+      </c>
+      <c r="B20" t="s">
+        <v>22</v>
+      </c>
+      <c r="C20" t="s">
+        <v>23</v>
+      </c>
+      <c r="D20" t="s">
+        <v>24</v>
+      </c>
+      <c r="F20" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>55</v>
+      </c>
+      <c r="B21" t="s">
+        <v>291</v>
+      </c>
+      <c r="C21" t="s">
+        <v>294</v>
+      </c>
+      <c r="D21" t="s">
+        <v>27</v>
+      </c>
+      <c r="E21" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>57</v>
+      </c>
+      <c r="B23" t="s">
+        <v>58</v>
+      </c>
+      <c r="C23" t="s">
+        <v>10</v>
+      </c>
+      <c r="D23" t="s">
+        <v>289</v>
+      </c>
+      <c r="E23" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>61</v>
+      </c>
+      <c r="B25" t="s">
+        <v>62</v>
+      </c>
+      <c r="C25" t="s">
+        <v>63</v>
+      </c>
+      <c r="D25" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>65</v>
+      </c>
+      <c r="B26" t="s">
+        <v>22</v>
+      </c>
+      <c r="C26" t="s">
+        <v>23</v>
+      </c>
+      <c r="D26" t="s">
+        <v>289</v>
+      </c>
+      <c r="E26" t="s">
+        <v>66</v>
+      </c>
+      <c r="F26" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>67</v>
+      </c>
+      <c r="B27" t="s">
+        <v>22</v>
+      </c>
+      <c r="C27" t="s">
+        <v>26</v>
+      </c>
+      <c r="D27" t="s">
+        <v>27</v>
+      </c>
+      <c r="E27" t="s">
+        <v>68</v>
+      </c>
+      <c r="F27" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>69</v>
+      </c>
+      <c r="B28" t="s">
+        <v>22</v>
+      </c>
+      <c r="C28" t="s">
+        <v>26</v>
+      </c>
+      <c r="D28" t="s">
+        <v>27</v>
+      </c>
+      <c r="E28" t="s">
+        <v>70</v>
+      </c>
+      <c r="F28" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>72</v>
+      </c>
+      <c r="B30" t="s">
+        <v>73</v>
+      </c>
+      <c r="C30" t="s">
+        <v>63</v>
+      </c>
+      <c r="D30" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>74</v>
+      </c>
+      <c r="B31" t="s">
+        <v>73</v>
+      </c>
+      <c r="C31" t="s">
+        <v>75</v>
+      </c>
+      <c r="D31" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>76</v>
+      </c>
+      <c r="F32" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>78</v>
+      </c>
+      <c r="F33" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>79</v>
+      </c>
+      <c r="B34" t="s">
+        <v>50</v>
+      </c>
+      <c r="C34" t="s">
+        <v>80</v>
+      </c>
+      <c r="D34" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>81</v>
+      </c>
+      <c r="B35" t="s">
+        <v>50</v>
+      </c>
+      <c r="C35" t="s">
+        <v>82</v>
+      </c>
+      <c r="D35" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>83</v>
+      </c>
+      <c r="B36" t="s">
+        <v>50</v>
+      </c>
+      <c r="C36" t="s">
+        <v>84</v>
+      </c>
+      <c r="D36" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>85</v>
+      </c>
+      <c r="B37" t="s">
+        <v>50</v>
+      </c>
+      <c r="C37" t="s">
+        <v>86</v>
+      </c>
+      <c r="D37" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>87</v>
+      </c>
+      <c r="B38" t="s">
+        <v>50</v>
+      </c>
+      <c r="C38" t="s">
+        <v>88</v>
+      </c>
+      <c r="D38" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>89</v>
+      </c>
+      <c r="B39" t="s">
+        <v>50</v>
+      </c>
+      <c r="C39" t="s">
+        <v>90</v>
+      </c>
+      <c r="D39" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>93</v>
+      </c>
+      <c r="B42" t="s">
+        <v>94</v>
+      </c>
+      <c r="C42" t="s">
+        <v>95</v>
+      </c>
+      <c r="D42" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>97</v>
+      </c>
+      <c r="B43" t="s">
+        <v>315</v>
+      </c>
+      <c r="C43" t="s">
+        <v>316</v>
+      </c>
+      <c r="D43" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>99</v>
+      </c>
+      <c r="B44" t="s">
+        <v>94</v>
+      </c>
+      <c r="C44" t="s">
+        <v>100</v>
+      </c>
+      <c r="D44" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>101</v>
+      </c>
+      <c r="B45" t="s">
+        <v>94</v>
+      </c>
+      <c r="C45" t="s">
+        <v>102</v>
+      </c>
+      <c r="D45" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>103</v>
+      </c>
+      <c r="B46" t="s">
+        <v>94</v>
+      </c>
+      <c r="C46" t="s">
+        <v>104</v>
+      </c>
+      <c r="D46" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>108</v>
+      </c>
+      <c r="B50" t="s">
+        <v>109</v>
+      </c>
+      <c r="C50" t="s">
+        <v>63</v>
+      </c>
+      <c r="D50" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>110</v>
+      </c>
+      <c r="B51" t="s">
+        <v>109</v>
+      </c>
+      <c r="C51" t="s">
+        <v>75</v>
+      </c>
+      <c r="D51" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>111</v>
+      </c>
+      <c r="B52" t="s">
+        <v>94</v>
+      </c>
+      <c r="C52" t="s">
+        <v>112</v>
+      </c>
+      <c r="D52" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>115</v>
+      </c>
+      <c r="B55" t="s">
+        <v>116</v>
+      </c>
+      <c r="C55" t="s">
+        <v>75</v>
+      </c>
+      <c r="D55" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>118</v>
+      </c>
+      <c r="B56" t="s">
+        <v>116</v>
+      </c>
+      <c r="C56" t="s">
+        <v>63</v>
+      </c>
+      <c r="D56" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>120</v>
+      </c>
+      <c r="B58" t="s">
+        <v>121</v>
+      </c>
+      <c r="C58" t="s">
+        <v>75</v>
+      </c>
+      <c r="D58" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>123</v>
+      </c>
+      <c r="B59" t="s">
+        <v>121</v>
+      </c>
+      <c r="C59" t="s">
+        <v>63</v>
+      </c>
+      <c r="D59" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>126</v>
+      </c>
+      <c r="B62" t="s">
+        <v>127</v>
+      </c>
+      <c r="C62" t="s">
+        <v>6</v>
+      </c>
+      <c r="D62" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>128</v>
+      </c>
+      <c r="B63" t="s">
+        <v>127</v>
+      </c>
+      <c r="C63" t="s">
+        <v>10</v>
+      </c>
+      <c r="D63" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>129</v>
+      </c>
+      <c r="B64" t="s">
+        <v>127</v>
+      </c>
+      <c r="C64" t="s">
+        <v>12</v>
+      </c>
+      <c r="D64" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>130</v>
+      </c>
+      <c r="B65" t="s">
+        <v>127</v>
+      </c>
+      <c r="C65" t="s">
+        <v>14</v>
+      </c>
+      <c r="D65" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>131</v>
+      </c>
+      <c r="B66" t="s">
+        <v>132</v>
+      </c>
+      <c r="C66" t="s">
+        <v>63</v>
+      </c>
+      <c r="D66" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>133</v>
+      </c>
+      <c r="B67" t="s">
+        <v>132</v>
+      </c>
+      <c r="C67" t="s">
+        <v>75</v>
+      </c>
+      <c r="D67" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>134</v>
+      </c>
+      <c r="B68" t="s">
+        <v>22</v>
+      </c>
+      <c r="C68" t="s">
+        <v>26</v>
+      </c>
+      <c r="D68" t="s">
+        <v>32</v>
+      </c>
+      <c r="E68" t="s">
+        <v>135</v>
+      </c>
+      <c r="F68" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>136</v>
+      </c>
+      <c r="B69" t="s">
+        <v>22</v>
+      </c>
+      <c r="C69" t="s">
+        <v>23</v>
+      </c>
+      <c r="D69" t="s">
+        <v>32</v>
+      </c>
+      <c r="E69" t="s">
+        <v>137</v>
+      </c>
+      <c r="F69" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>138</v>
+      </c>
+      <c r="B70" t="s">
+        <v>139</v>
+      </c>
+      <c r="C70" t="s">
+        <v>140</v>
+      </c>
+      <c r="D70" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>141</v>
+      </c>
+      <c r="B71" t="s">
+        <v>139</v>
+      </c>
+      <c r="C71" t="s">
+        <v>142</v>
+      </c>
+      <c r="D71" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>143</v>
+      </c>
+      <c r="B72" t="s">
+        <v>139</v>
+      </c>
+      <c r="C72" t="s">
+        <v>28</v>
+      </c>
+      <c r="D72" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>144</v>
+      </c>
+      <c r="B73" t="s">
+        <v>145</v>
+      </c>
+      <c r="C73" t="s">
+        <v>63</v>
+      </c>
+      <c r="D73" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>146</v>
+      </c>
+      <c r="B74" t="s">
+        <v>145</v>
+      </c>
+      <c r="C74" t="s">
+        <v>75</v>
+      </c>
+      <c r="D74" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>149</v>
+      </c>
+      <c r="B77" t="s">
+        <v>22</v>
+      </c>
+      <c r="C77" t="s">
+        <v>26</v>
+      </c>
+      <c r="D77" t="s">
+        <v>150</v>
+      </c>
+      <c r="E77" t="s">
+        <v>151</v>
+      </c>
+      <c r="F77" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>152</v>
+      </c>
+      <c r="B78" t="s">
+        <v>139</v>
+      </c>
+      <c r="C78" t="s">
+        <v>153</v>
+      </c>
+      <c r="D78" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>154</v>
+      </c>
+      <c r="B79" t="s">
+        <v>34</v>
+      </c>
+      <c r="C79" t="s">
+        <v>12</v>
+      </c>
+      <c r="D79" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>155</v>
+      </c>
+      <c r="B80" t="s">
+        <v>34</v>
+      </c>
+      <c r="C80" t="s">
+        <v>14</v>
+      </c>
+      <c r="D80" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>156</v>
+      </c>
+      <c r="B81" t="s">
+        <v>22</v>
+      </c>
+      <c r="C81" t="s">
+        <v>23</v>
+      </c>
+      <c r="D81" t="s">
+        <v>96</v>
+      </c>
+      <c r="E81" t="s">
+        <v>318</v>
+      </c>
+      <c r="F81" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>157</v>
+      </c>
+      <c r="B82" t="s">
+        <v>158</v>
+      </c>
+      <c r="C82" t="s">
+        <v>98</v>
+      </c>
+      <c r="D82" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>159</v>
+      </c>
+      <c r="B83" t="s">
+        <v>158</v>
+      </c>
+      <c r="C83" t="s">
+        <v>31</v>
+      </c>
+      <c r="D83" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>163</v>
+      </c>
+      <c r="B86" t="s">
+        <v>162</v>
+      </c>
+      <c r="C86" t="s">
+        <v>88</v>
+      </c>
+      <c r="D86" t="s">
+        <v>306</v>
+      </c>
+      <c r="E86" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
+        <v>164</v>
+      </c>
+      <c r="B87" t="s">
+        <v>162</v>
+      </c>
+      <c r="C87" t="s">
+        <v>90</v>
+      </c>
+      <c r="D87" t="s">
+        <v>306</v>
+      </c>
+      <c r="E87" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>165</v>
+      </c>
+      <c r="B88" t="s">
+        <v>166</v>
+      </c>
+      <c r="C88" t="s">
+        <v>140</v>
+      </c>
+      <c r="D88" t="s">
+        <v>289</v>
+      </c>
+      <c r="E88" t="s">
+        <v>290</v>
+      </c>
+      <c r="F88" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
+        <v>167</v>
+      </c>
+      <c r="B89" t="s">
+        <v>166</v>
+      </c>
+      <c r="C89" t="s">
+        <v>153</v>
+      </c>
+      <c r="D89" t="s">
+        <v>289</v>
+      </c>
+      <c r="E89" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
+        <v>168</v>
+      </c>
+      <c r="B90" t="s">
+        <v>166</v>
+      </c>
+      <c r="C90" t="s">
+        <v>142</v>
+      </c>
+      <c r="D90" t="s">
+        <v>289</v>
+      </c>
+      <c r="E90" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
+        <v>169</v>
+      </c>
+      <c r="B91" t="s">
+        <v>166</v>
+      </c>
+      <c r="C91" t="s">
+        <v>28</v>
+      </c>
+      <c r="D91" t="s">
+        <v>289</v>
+      </c>
+      <c r="E91" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
+        <v>170</v>
+      </c>
+      <c r="B92" t="s">
+        <v>162</v>
+      </c>
+      <c r="C92" t="s">
+        <v>51</v>
+      </c>
+      <c r="D92" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
+        <v>175</v>
+      </c>
+      <c r="B96" t="s">
+        <v>22</v>
+      </c>
+      <c r="C96" t="s">
+        <v>26</v>
+      </c>
+      <c r="D96" t="s">
+        <v>150</v>
+      </c>
+      <c r="E96" t="s">
+        <v>176</v>
+      </c>
+      <c r="F96" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A106" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A107" t="s">
+        <v>187</v>
+      </c>
+      <c r="B107" t="s">
+        <v>188</v>
+      </c>
+      <c r="C107" t="s">
+        <v>63</v>
+      </c>
+      <c r="D107" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A108" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A109" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A110" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A111" t="s">
+        <v>193</v>
+      </c>
+      <c r="B111" t="s">
+        <v>22</v>
+      </c>
+      <c r="C111" t="s">
+        <v>26</v>
+      </c>
+      <c r="D111" t="s">
+        <v>308</v>
+      </c>
+      <c r="E111" t="s">
+        <v>194</v>
+      </c>
+      <c r="F111" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A112" t="s">
+        <v>195</v>
+      </c>
+      <c r="B112" t="s">
+        <v>188</v>
+      </c>
+      <c r="C112" t="s">
+        <v>75</v>
+      </c>
+      <c r="D112" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A113" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A114" t="s">
+        <v>197</v>
+      </c>
+      <c r="B114" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A115" t="s">
+        <v>199</v>
+      </c>
+      <c r="B115" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A116" t="s">
+        <v>200</v>
+      </c>
+      <c r="B116" t="s">
+        <v>22</v>
+      </c>
+      <c r="C116" t="s">
+        <v>26</v>
+      </c>
+      <c r="D116" t="s">
+        <v>201</v>
+      </c>
+      <c r="F116" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A117" t="s">
+        <v>202</v>
+      </c>
+      <c r="B117" t="s">
+        <v>22</v>
+      </c>
+      <c r="C117" t="s">
+        <v>26</v>
+      </c>
+      <c r="D117" t="s">
+        <v>201</v>
+      </c>
+      <c r="F117" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A118" t="s">
+        <v>203</v>
+      </c>
+      <c r="B118" t="s">
+        <v>22</v>
+      </c>
+      <c r="C118" t="s">
+        <v>26</v>
+      </c>
+      <c r="D118" t="s">
+        <v>201</v>
+      </c>
+      <c r="F118" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A119" t="s">
+        <v>204</v>
+      </c>
+      <c r="B119" t="s">
+        <v>22</v>
+      </c>
+      <c r="C119" t="s">
+        <v>26</v>
+      </c>
+      <c r="D119" t="s">
+        <v>201</v>
+      </c>
+      <c r="F119" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A120" t="s">
+        <v>205</v>
+      </c>
+      <c r="B120" t="s">
+        <v>206</v>
+      </c>
+      <c r="C120" t="s">
+        <v>6</v>
+      </c>
+      <c r="D120" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A121" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A122" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A123" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A124" t="s">
+        <v>212</v>
+      </c>
+      <c r="B124" t="s">
+        <v>213</v>
+      </c>
+      <c r="C124" t="s">
+        <v>6</v>
+      </c>
+      <c r="D124" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A125" t="s">
+        <v>215</v>
+      </c>
+      <c r="B125" t="s">
+        <v>213</v>
+      </c>
+      <c r="C125" t="s">
+        <v>10</v>
+      </c>
+      <c r="D125" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A126" t="s">
+        <v>216</v>
+      </c>
+      <c r="B126" t="s">
+        <v>213</v>
+      </c>
+      <c r="C126" t="s">
+        <v>12</v>
+      </c>
+      <c r="D126" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A127" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A128" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A129" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A130" t="s">
+        <v>220</v>
+      </c>
+      <c r="B130" t="s">
+        <v>213</v>
+      </c>
+      <c r="C130" t="s">
+        <v>14</v>
+      </c>
+      <c r="D130" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A131" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A132" t="s">
+        <v>222</v>
+      </c>
+      <c r="B132" t="s">
+        <v>223</v>
+      </c>
+      <c r="C132" t="s">
+        <v>14</v>
+      </c>
+      <c r="D132" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A133" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A134" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A135" t="s">
+        <v>226</v>
+      </c>
+      <c r="B135" t="s">
+        <v>223</v>
+      </c>
+      <c r="C135" t="s">
+        <v>6</v>
+      </c>
+      <c r="D135" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A136" t="s">
+        <v>227</v>
+      </c>
+      <c r="B136" t="s">
+        <v>223</v>
+      </c>
+      <c r="C136" t="s">
+        <v>10</v>
+      </c>
+      <c r="D136" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A137" t="s">
         <v>228</v>
+      </c>
+      <c r="B137" t="s">
+        <v>223</v>
+      </c>
+      <c r="C137" t="s">
+        <v>12</v>
+      </c>
+      <c r="D137" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A138" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A139" t="s">
+        <v>230</v>
+      </c>
+      <c r="B139" t="s">
+        <v>22</v>
+      </c>
+      <c r="C139" t="s">
+        <v>23</v>
+      </c>
+      <c r="D139" t="s">
+        <v>307</v>
+      </c>
+      <c r="E139" t="s">
+        <v>323</v>
+      </c>
+      <c r="F139" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A140" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A141" t="s">
+        <v>233</v>
       </c>
     </row>
   </sheetData>

--- a/.doc/官方手册/引脚映射表.xlsx
+++ b/.doc/官方手册/引脚映射表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\itgz2\Desktop\BetaRobot\.doc\官方手册\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC764761-503E-4A48-B4C2-6576AE2DC394}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{741C54BA-5D15-47FE-8E7A-5D18F75105B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="DJI_A" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">DJI_A!$A$1:$F$141</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">DJI_A!$A$1:$G$141</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">DJI_C!$D$1:$D$141</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">DM_MC02!$A$1:$G$81</definedName>
   </definedNames>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1175" uniqueCount="324">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1197" uniqueCount="329">
   <si>
     <t>Port-Pin</t>
   </si>
@@ -1032,6 +1032,24 @@
   </si>
   <si>
     <t>DAC_EXTI</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>180MHZ/(59+1)*(59999+1)=50HZ</t>
+  </si>
+  <si>
+    <t>180MHZ/(59+1)*(59999+1)=50HZ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>90MHZ/(29+1)*(59999+1)=50HZ</t>
+  </si>
+  <si>
+    <t>90MHZ/(29+1)*(59999+1)=50HZ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>90MHZ/(0+1)*(22499+1)=4KHZ</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2760,7 +2778,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G81" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4264,7 +4281,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="D1:D141" xr:uid="{00000000-0001-0000-0200-000000000000}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4272,7 +4288,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:F141"/>
+  <dimension ref="A1:G141"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="10" customWidth="1"/>
@@ -4282,7 +4298,7 @@
     <col min="6" max="6" width="31" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4302,7 +4318,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -4315,8 +4331,14 @@
       <c r="D2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F2" t="s">
+        <v>327</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -4329,8 +4351,14 @@
       <c r="D3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F3" t="s">
+        <v>327</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -4343,8 +4371,14 @@
       <c r="D4" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F4" t="s">
+        <v>327</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -4357,8 +4391,14 @@
       <c r="D5" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F5" t="s">
+        <v>327</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -4372,7 +4412,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -4386,7 +4426,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -4405,8 +4445,11 @@
       <c r="F8" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>25</v>
       </c>
@@ -4423,7 +4466,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>29</v>
       </c>
@@ -4436,8 +4479,14 @@
       <c r="D10" t="s">
         <v>312</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F10" t="s">
+        <v>325</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>33</v>
       </c>
@@ -4450,8 +4499,14 @@
       <c r="D11" t="s">
         <v>312</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F11" t="s">
+        <v>325</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>35</v>
       </c>
@@ -4465,7 +4520,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>38</v>
       </c>
@@ -4479,7 +4534,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>40</v>
       </c>
@@ -4493,7 +4548,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>42</v>
       </c>
@@ -4506,8 +4561,11 @@
       <c r="D15" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>46</v>
       </c>
@@ -4520,13 +4578,16 @@
       <c r="D16" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>49</v>
       </c>
@@ -4539,8 +4600,11 @@
       <c r="D18" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>52</v>
       </c>
@@ -4553,8 +4617,11 @@
       <c r="D19" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>54</v>
       </c>
@@ -4570,8 +4637,11 @@
       <c r="F20" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>55</v>
       </c>
@@ -4588,12 +4658,12 @@
         <v>294</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>57</v>
       </c>
@@ -4609,13 +4679,19 @@
       <c r="E23" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F23" t="s">
+        <v>328</v>
+      </c>
+      <c r="G23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>61</v>
       </c>
@@ -4628,8 +4704,11 @@
       <c r="D25" t="s">
         <v>314</v>
       </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>65</v>
       </c>
@@ -4648,8 +4727,11 @@
       <c r="F26" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>67</v>
       </c>
@@ -4668,8 +4750,11 @@
       <c r="F27" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>69</v>
       </c>
@@ -4688,13 +4773,16 @@
       <c r="F28" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>72</v>
       </c>
@@ -4708,7 +4796,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>74</v>
       </c>
@@ -4722,7 +4810,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>76</v>
       </c>
@@ -4730,7 +4818,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>78</v>
       </c>
@@ -4738,7 +4826,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>79</v>
       </c>
@@ -4751,8 +4839,11 @@
       <c r="D34" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>81</v>
       </c>
@@ -4765,8 +4856,11 @@
       <c r="D35" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>83</v>
       </c>
@@ -4779,8 +4873,11 @@
       <c r="D36" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>85</v>
       </c>
@@ -4793,8 +4890,11 @@
       <c r="D37" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>87</v>
       </c>
@@ -4807,8 +4907,11 @@
       <c r="D38" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>89</v>
       </c>
@@ -4821,18 +4924,21 @@
       <c r="D39" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>93</v>
       </c>
@@ -4846,7 +4952,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>97</v>
       </c>
@@ -4860,7 +4966,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>99</v>
       </c>
@@ -4874,7 +4980,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>101</v>
       </c>
@@ -4888,7 +4994,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>103</v>
       </c>
@@ -4902,22 +5008,22 @@
         <v>96</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>108</v>
       </c>
@@ -4931,7 +5037,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>110</v>
       </c>
@@ -4945,7 +5051,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>111</v>
       </c>
@@ -4959,17 +5065,17 @@
         <v>96</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>115</v>
       </c>
@@ -4983,7 +5089,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>118</v>
       </c>
@@ -4997,12 +5103,12 @@
         <v>117</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>120</v>
       </c>
@@ -5016,7 +5122,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>123</v>
       </c>
@@ -5030,17 +5136,17 @@
         <v>122</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>126</v>
       </c>
@@ -5053,8 +5159,14 @@
       <c r="D62" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F62" t="s">
+        <v>326</v>
+      </c>
+      <c r="G62">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>128</v>
       </c>
@@ -5067,8 +5179,14 @@
       <c r="D63" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="F63" t="s">
+        <v>326</v>
+      </c>
+      <c r="G63">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>129</v>
       </c>
@@ -5081,8 +5199,14 @@
       <c r="D64" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F64" t="s">
+        <v>326</v>
+      </c>
+      <c r="G64">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>130</v>
       </c>
@@ -5095,8 +5219,14 @@
       <c r="D65" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F65" t="s">
+        <v>326</v>
+      </c>
+      <c r="G65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>131</v>
       </c>
@@ -5110,7 +5240,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>133</v>
       </c>
@@ -5124,7 +5254,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>134</v>
       </c>
@@ -5143,8 +5273,11 @@
       <c r="F68" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G68">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>136</v>
       </c>
@@ -5163,8 +5296,11 @@
       <c r="F69" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G69">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>138</v>
       </c>
@@ -5178,7 +5314,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>141</v>
       </c>
@@ -5192,7 +5328,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>143</v>
       </c>
@@ -5206,7 +5342,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>144</v>
       </c>
@@ -5220,7 +5356,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>146</v>
       </c>
@@ -5234,17 +5370,17 @@
         <v>145</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>149</v>
       </c>
@@ -5263,8 +5399,11 @@
       <c r="F77" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>152</v>
       </c>
@@ -5278,7 +5417,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>154</v>
       </c>
@@ -5291,8 +5430,14 @@
       <c r="D79" t="s">
         <v>312</v>
       </c>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F79" t="s">
+        <v>325</v>
+      </c>
+      <c r="G79">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>155</v>
       </c>
@@ -5305,8 +5450,14 @@
       <c r="D80" t="s">
         <v>312</v>
       </c>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F80" t="s">
+        <v>325</v>
+      </c>
+      <c r="G80">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>156</v>
       </c>
@@ -5325,8 +5476,11 @@
       <c r="F81" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G81">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>157</v>
       </c>
@@ -5340,7 +5494,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>159</v>
       </c>
@@ -5354,17 +5508,17 @@
         <v>18</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>163</v>
       </c>
@@ -5380,8 +5534,11 @@
       <c r="E86" t="s">
         <v>319</v>
       </c>
-    </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G86">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>164</v>
       </c>
@@ -5397,8 +5554,11 @@
       <c r="E87" t="s">
         <v>320</v>
       </c>
-    </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G87">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>165</v>
       </c>
@@ -5418,7 +5578,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>167</v>
       </c>
@@ -5435,7 +5595,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>168</v>
       </c>
@@ -5452,7 +5612,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>169</v>
       </c>
@@ -5469,7 +5629,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>170</v>
       </c>
@@ -5482,23 +5642,26 @@
       <c r="D92" t="s">
         <v>307</v>
       </c>
-    </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G92">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>175</v>
       </c>
@@ -5517,58 +5680,61 @@
       <c r="F96" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G96">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>187</v>
       </c>
@@ -5582,22 +5748,22 @@
         <v>321</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>193</v>
       </c>
@@ -5616,8 +5782,11 @@
       <c r="F111" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G111">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>195</v>
       </c>
@@ -5631,28 +5800,34 @@
         <v>321</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>197</v>
       </c>
       <c r="B114" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G114">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>199</v>
       </c>
       <c r="B115" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G115">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>200</v>
       </c>
@@ -5668,8 +5843,11 @@
       <c r="F116" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G116">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>202</v>
       </c>
@@ -5685,8 +5863,11 @@
       <c r="F117" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G117">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>203</v>
       </c>
@@ -5702,8 +5883,11 @@
       <c r="F118" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G118">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>204</v>
       </c>
@@ -5719,8 +5903,11 @@
       <c r="F119" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G119">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>205</v>
       </c>
@@ -5733,23 +5920,29 @@
       <c r="D120" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F120" t="s">
+        <v>328</v>
+      </c>
+      <c r="G120">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>212</v>
       </c>
@@ -5762,8 +5955,14 @@
       <c r="D124" t="s">
         <v>322</v>
       </c>
-    </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F124" t="s">
+        <v>326</v>
+      </c>
+      <c r="G124">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>215</v>
       </c>
@@ -5776,8 +5975,14 @@
       <c r="D125" t="s">
         <v>322</v>
       </c>
-    </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F125" t="s">
+        <v>326</v>
+      </c>
+      <c r="G125">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>216</v>
       </c>
@@ -5790,23 +5995,29 @@
       <c r="D126" t="s">
         <v>322</v>
       </c>
-    </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F126" t="s">
+        <v>326</v>
+      </c>
+      <c r="G126">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>220</v>
       </c>
@@ -5819,13 +6030,19 @@
       <c r="D130" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F130" t="s">
+        <v>326</v>
+      </c>
+      <c r="G130">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>222</v>
       </c>
@@ -5838,18 +6055,24 @@
       <c r="D132" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F132" t="s">
+        <v>324</v>
+      </c>
+      <c r="G132">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>226</v>
       </c>
@@ -5862,8 +6085,14 @@
       <c r="D135" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F135" t="s">
+        <v>324</v>
+      </c>
+      <c r="G135">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>227</v>
       </c>
@@ -5876,8 +6105,14 @@
       <c r="D136" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F136" t="s">
+        <v>324</v>
+      </c>
+      <c r="G136">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>228</v>
       </c>
@@ -5890,13 +6125,19 @@
       <c r="D137" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F137" t="s">
+        <v>324</v>
+      </c>
+      <c r="G137">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>230</v>
       </c>
@@ -5915,13 +6156,16 @@
       <c r="F139" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G139">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>233</v>
       </c>

--- a/.doc/官方手册/引脚映射表.xlsx
+++ b/.doc/官方手册/引脚映射表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\itgz2\Desktop\BetaRobot\.doc\官方手册\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{741C54BA-5D15-47FE-8E7A-5D18F75105B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCE74747-54F0-449B-B576-E592791FFFB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DM_MC02" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">DJI_A!$A$1:$G$141</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">DJI_C!$D$1:$D$141</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">DJI_C!$A$1:$G$141</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">DM_MC02!$A$1:$G$81</definedName>
   </definedNames>
   <calcPr calcId="0"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1197" uniqueCount="329">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1198" uniqueCount="330">
   <si>
     <t>Port-Pin</t>
   </si>
@@ -1050,6 +1050,10 @@
   </si>
   <si>
     <t>90MHZ/(0+1)*(22499+1)=4KHZ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>?</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1635,6 +1639,9 @@
       <c r="D11" t="s">
         <v>64</v>
       </c>
+      <c r="G11" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
@@ -1649,6 +1656,9 @@
       <c r="D12" t="s">
         <v>64</v>
       </c>
+      <c r="G12" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
@@ -1799,6 +1809,9 @@
       <c r="D21" t="s">
         <v>242</v>
       </c>
+      <c r="G21" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
@@ -1813,6 +1826,9 @@
       <c r="D22" t="s">
         <v>242</v>
       </c>
+      <c r="G22" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
@@ -1827,6 +1843,9 @@
       <c r="D23" t="s">
         <v>73</v>
       </c>
+      <c r="G23" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
@@ -1841,6 +1860,9 @@
       <c r="D24" t="s">
         <v>73</v>
       </c>
+      <c r="G24" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
@@ -1897,6 +1919,9 @@
       <c r="D28" t="s">
         <v>242</v>
       </c>
+      <c r="G28" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
@@ -1911,6 +1936,9 @@
       <c r="D29" t="s">
         <v>242</v>
       </c>
+      <c r="G29" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
@@ -1959,6 +1987,9 @@
       <c r="D32" t="s">
         <v>261</v>
       </c>
+      <c r="G32" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
@@ -2276,6 +2307,9 @@
       <c r="D50" t="s">
         <v>109</v>
       </c>
+      <c r="G50" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
@@ -2290,6 +2324,9 @@
       <c r="D51" t="s">
         <v>109</v>
       </c>
+      <c r="G51" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
@@ -2338,6 +2375,9 @@
       <c r="D54" t="s">
         <v>272</v>
       </c>
+      <c r="G54" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
@@ -2352,6 +2392,9 @@
       <c r="D55" t="s">
         <v>272</v>
       </c>
+      <c r="G55" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
@@ -2366,6 +2409,9 @@
       <c r="D56" t="s">
         <v>272</v>
       </c>
+      <c r="G56" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
@@ -2380,6 +2426,9 @@
       <c r="D57" t="s">
         <v>242</v>
       </c>
+      <c r="G57" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
@@ -2394,6 +2443,9 @@
       <c r="D58" t="s">
         <v>261</v>
       </c>
+      <c r="G58" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
@@ -2408,6 +2460,9 @@
       <c r="D59" t="s">
         <v>261</v>
       </c>
+      <c r="G59" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
@@ -2459,6 +2514,9 @@
       <c r="D62" t="s">
         <v>274</v>
       </c>
+      <c r="G62" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
@@ -2473,6 +2531,9 @@
       <c r="D63" t="s">
         <v>274</v>
       </c>
+      <c r="G63" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
@@ -2490,6 +2551,9 @@
       <c r="E64" t="s">
         <v>275</v>
       </c>
+      <c r="G64" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
@@ -2507,6 +2571,9 @@
       <c r="E65" t="s">
         <v>275</v>
       </c>
+      <c r="G65" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
@@ -2524,6 +2591,9 @@
       <c r="E66" t="s">
         <v>132</v>
       </c>
+      <c r="G66" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
@@ -2541,6 +2611,9 @@
       <c r="E67" t="s">
         <v>132</v>
       </c>
+      <c r="G67" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
@@ -2555,6 +2628,9 @@
       <c r="D68" t="s">
         <v>277</v>
       </c>
+      <c r="G68" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
@@ -2569,6 +2645,9 @@
       <c r="D69" t="s">
         <v>277</v>
       </c>
+      <c r="G69" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
@@ -2625,6 +2704,9 @@
       <c r="D73" t="s">
         <v>145</v>
       </c>
+      <c r="G73" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
@@ -2639,6 +2721,9 @@
       <c r="D74" t="s">
         <v>145</v>
       </c>
+      <c r="G74" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
@@ -2763,7 +2848,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>156</v>
       </c>
@@ -2775,6 +2860,9 @@
       </c>
       <c r="D81" t="s">
         <v>242</v>
+      </c>
+      <c r="G81" s="1" t="s">
+        <v>329</v>
       </c>
     </row>
   </sheetData>
@@ -2946,6 +3034,9 @@
         <v>64</v>
       </c>
       <c r="F11"/>
+      <c r="G11">
+        <v>1</v>
+      </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
@@ -3116,6 +3207,9 @@
         <v>73</v>
       </c>
       <c r="F23"/>
+      <c r="G23">
+        <v>1</v>
+      </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
@@ -3131,6 +3225,9 @@
         <v>73</v>
       </c>
       <c r="F24"/>
+      <c r="G24">
+        <v>1</v>
+      </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
@@ -3146,6 +3243,9 @@
         <v>64</v>
       </c>
       <c r="F25"/>
+      <c r="G25">
+        <v>1</v>
+      </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
@@ -3207,6 +3307,9 @@
         <v>18</v>
       </c>
       <c r="F30"/>
+      <c r="G30">
+        <v>1</v>
+      </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
@@ -3222,6 +3325,9 @@
         <v>18</v>
       </c>
       <c r="F31"/>
+      <c r="G31">
+        <v>1</v>
+      </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
@@ -3237,6 +3343,9 @@
         <v>18</v>
       </c>
       <c r="F32"/>
+      <c r="G32">
+        <v>1</v>
+      </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
@@ -3252,6 +3361,9 @@
         <v>18</v>
       </c>
       <c r="F33"/>
+      <c r="G33">
+        <v>1</v>
+      </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
@@ -3452,6 +3564,9 @@
         <v>109</v>
       </c>
       <c r="F50"/>
+      <c r="G50">
+        <v>1</v>
+      </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
@@ -3467,6 +3582,9 @@
         <v>109</v>
       </c>
       <c r="F51"/>
+      <c r="G51">
+        <v>1</v>
+      </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
@@ -3757,6 +3875,9 @@
         <v>18</v>
       </c>
       <c r="F82"/>
+      <c r="G82">
+        <v>1</v>
+      </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
@@ -3772,6 +3893,9 @@
         <v>18</v>
       </c>
       <c r="F83"/>
+      <c r="G83">
+        <v>1</v>
+      </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
@@ -3972,6 +4096,9 @@
         <v>189</v>
       </c>
       <c r="F107"/>
+      <c r="G107">
+        <v>1</v>
+      </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
@@ -4007,6 +4134,9 @@
         <v>189</v>
       </c>
       <c r="F112"/>
+      <c r="G112">
+        <v>1</v>
+      </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
@@ -4411,6 +4541,9 @@
       <c r="D6" t="s">
         <v>18</v>
       </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
@@ -4425,6 +4558,9 @@
       <c r="D7" t="s">
         <v>18</v>
       </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
@@ -4465,6 +4601,9 @@
       <c r="E9" t="s">
         <v>28</v>
       </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
@@ -4657,6 +4796,9 @@
       <c r="E21" t="s">
         <v>294</v>
       </c>
+      <c r="G21">
+        <v>1</v>
+      </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
@@ -4795,6 +4937,9 @@
       <c r="D30" t="s">
         <v>73</v>
       </c>
+      <c r="G30">
+        <v>1</v>
+      </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
@@ -4809,6 +4954,9 @@
       <c r="D31" t="s">
         <v>73</v>
       </c>
+      <c r="G31">
+        <v>1</v>
+      </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
@@ -4817,6 +4965,9 @@
       <c r="F32" t="s">
         <v>309</v>
       </c>
+      <c r="G32">
+        <v>1</v>
+      </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
@@ -4825,6 +4976,9 @@
       <c r="F33" t="s">
         <v>309</v>
       </c>
+      <c r="G33">
+        <v>1</v>
+      </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
@@ -5036,6 +5190,9 @@
       <c r="D50" t="s">
         <v>109</v>
       </c>
+      <c r="G50">
+        <v>1</v>
+      </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
@@ -5050,6 +5207,9 @@
       <c r="D51" t="s">
         <v>109</v>
       </c>
+      <c r="G51">
+        <v>1</v>
+      </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
@@ -5088,6 +5248,9 @@
       <c r="D55" t="s">
         <v>117</v>
       </c>
+      <c r="G55">
+        <v>1</v>
+      </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
@@ -5102,6 +5265,9 @@
       <c r="D56" t="s">
         <v>117</v>
       </c>
+      <c r="G56">
+        <v>1</v>
+      </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
@@ -5121,6 +5287,9 @@
       <c r="D58" t="s">
         <v>122</v>
       </c>
+      <c r="G58">
+        <v>1</v>
+      </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
@@ -5135,6 +5304,9 @@
       <c r="D59" t="s">
         <v>122</v>
       </c>
+      <c r="G59">
+        <v>1</v>
+      </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
@@ -5239,6 +5411,9 @@
       <c r="D66" t="s">
         <v>132</v>
       </c>
+      <c r="G66">
+        <v>1</v>
+      </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
@@ -5253,6 +5428,9 @@
       <c r="D67" t="s">
         <v>132</v>
       </c>
+      <c r="G67">
+        <v>1</v>
+      </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
@@ -5313,6 +5491,9 @@
       <c r="D70" t="s">
         <v>18</v>
       </c>
+      <c r="G70">
+        <v>1</v>
+      </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
@@ -5327,6 +5508,9 @@
       <c r="D71" t="s">
         <v>18</v>
       </c>
+      <c r="G71">
+        <v>1</v>
+      </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
@@ -5341,6 +5525,9 @@
       <c r="D72" t="s">
         <v>18</v>
       </c>
+      <c r="G72">
+        <v>1</v>
+      </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
@@ -5355,6 +5542,9 @@
       <c r="D73" t="s">
         <v>145</v>
       </c>
+      <c r="G73">
+        <v>1</v>
+      </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
@@ -5369,6 +5559,9 @@
       <c r="D74" t="s">
         <v>145</v>
       </c>
+      <c r="G74">
+        <v>1</v>
+      </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
@@ -5416,6 +5609,9 @@
       <c r="D78" t="s">
         <v>18</v>
       </c>
+      <c r="G78">
+        <v>1</v>
+      </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
@@ -5493,6 +5689,9 @@
       <c r="D82" t="s">
         <v>18</v>
       </c>
+      <c r="G82">
+        <v>1</v>
+      </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
@@ -5507,6 +5706,9 @@
       <c r="D83" t="s">
         <v>18</v>
       </c>
+      <c r="G83">
+        <v>1</v>
+      </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
@@ -5577,6 +5779,9 @@
       <c r="F88" t="s">
         <v>26</v>
       </c>
+      <c r="G88">
+        <v>1</v>
+      </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
@@ -5594,6 +5799,9 @@
       <c r="E89" t="s">
         <v>153</v>
       </c>
+      <c r="G89">
+        <v>1</v>
+      </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
@@ -5611,6 +5819,9 @@
       <c r="E90" t="s">
         <v>142</v>
       </c>
+      <c r="G90">
+        <v>1</v>
+      </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
@@ -5628,6 +5839,9 @@
       <c r="E91" t="s">
         <v>28</v>
       </c>
+      <c r="G91">
+        <v>1</v>
+      </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
@@ -5747,6 +5961,9 @@
       <c r="D107" t="s">
         <v>321</v>
       </c>
+      <c r="G107">
+        <v>1</v>
+      </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
@@ -5798,6 +6015,9 @@
       </c>
       <c r="D112" t="s">
         <v>321</v>
+      </c>
+      <c r="G112">
+        <v>1</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.3">

--- a/.doc/官方手册/引脚映射表.xlsx
+++ b/.doc/官方手册/引脚映射表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\itgz2\Desktop\BetaRobot\.doc\官方手册\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCE74747-54F0-449B-B576-E592791FFFB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB824936-890F-4EE1-A545-4534AB337648}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DM_MC02" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1198" uniqueCount="330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1198" uniqueCount="329">
   <si>
     <t>Port-Pin</t>
   </si>
@@ -873,9 +873,6 @@
   </si>
   <si>
     <t>P1_NCS</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
   </si>
   <si>
     <t>CS</t>
@@ -1461,10 +1458,10 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
+        <v>294</v>
+      </c>
+      <c r="E1" t="s">
         <v>295</v>
-      </c>
-      <c r="E1" t="s">
-        <v>296</v>
       </c>
       <c r="F1" t="s">
         <v>3</v>
@@ -1623,7 +1620,7 @@
         <v>241</v>
       </c>
       <c r="E10" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
@@ -2025,7 +2022,7 @@
         <v>252</v>
       </c>
       <c r="E34" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F34" t="s">
         <v>26</v>
@@ -2084,7 +2081,7 @@
         <v>252</v>
       </c>
       <c r="E37" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F37" t="s">
         <v>26</v>
@@ -2104,7 +2101,7 @@
         <v>263</v>
       </c>
       <c r="D38" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E38" t="s">
         <v>171</v>
@@ -2236,7 +2233,7 @@
         <v>26</v>
       </c>
       <c r="D47" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E47" t="s">
         <v>201</v>
@@ -2259,7 +2256,7 @@
         <v>26</v>
       </c>
       <c r="D48" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E48" t="s">
         <v>201</v>
@@ -2759,7 +2756,7 @@
         <v>252</v>
       </c>
       <c r="E76" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F76" t="s">
         <v>23</v>
@@ -2796,7 +2793,7 @@
         <v>252</v>
       </c>
       <c r="E78" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F78" t="s">
         <v>23</v>
@@ -2810,7 +2807,7 @@
         <v>154</v>
       </c>
       <c r="B79" t="s">
-        <v>282</v>
+        <v>321</v>
       </c>
       <c r="C79" t="s">
         <v>12</v>
@@ -2856,13 +2853,13 @@
         <v>254</v>
       </c>
       <c r="C81" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D81" t="s">
         <v>242</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
   </sheetData>
@@ -2894,10 +2891,10 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
+        <v>294</v>
+      </c>
+      <c r="E1" t="s">
         <v>295</v>
-      </c>
-      <c r="E1" t="s">
-        <v>296</v>
       </c>
       <c r="F1" t="s">
         <v>3</v>
@@ -2952,7 +2949,7 @@
         <v>252</v>
       </c>
       <c r="E6" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F6" t="s">
         <v>26</v>
@@ -2977,10 +2974,10 @@
         <v>6</v>
       </c>
       <c r="D8" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="E8" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F8"/>
     </row>
@@ -3138,7 +3135,7 @@
         <v>252</v>
       </c>
       <c r="E18" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F18" t="s">
         <v>26</v>
@@ -3252,7 +3249,7 @@
         <v>65</v>
       </c>
       <c r="B26" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C26" t="s">
         <v>31</v>
@@ -3270,7 +3267,7 @@
         <v>67</v>
       </c>
       <c r="B27" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C27" t="s">
         <v>98</v>
@@ -3301,7 +3298,7 @@
         <v>258</v>
       </c>
       <c r="C30" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D30" t="s">
         <v>18</v>
@@ -3399,7 +3396,7 @@
         <v>252</v>
       </c>
       <c r="E38" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F38" t="s">
         <v>23</v>
@@ -3422,7 +3419,7 @@
         <v>252</v>
       </c>
       <c r="E39" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F39" t="s">
         <v>23</v>
@@ -3477,7 +3474,7 @@
         <v>12</v>
       </c>
       <c r="D42" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E42" t="s">
         <v>194</v>
@@ -3922,7 +3919,7 @@
         <v>165</v>
       </c>
       <c r="B88" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C88" t="s">
         <v>6</v>
@@ -3966,7 +3963,7 @@
         <v>51</v>
       </c>
       <c r="D92" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E92" t="s">
         <v>171</v>
@@ -4203,7 +4200,7 @@
         <v>239</v>
       </c>
       <c r="C122" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D122" t="s">
         <v>241</v>
@@ -4439,10 +4436,10 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
+        <v>294</v>
+      </c>
+      <c r="E1" t="s">
         <v>295</v>
-      </c>
-      <c r="E1" t="s">
-        <v>296</v>
       </c>
       <c r="F1" t="s">
         <v>3</v>
@@ -4462,7 +4459,7 @@
         <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -4482,7 +4479,7 @@
         <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="G3">
         <v>1</v>
@@ -4502,7 +4499,7 @@
         <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="G4">
         <v>1</v>
@@ -4522,7 +4519,7 @@
         <v>7</v>
       </c>
       <c r="F5" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -4573,10 +4570,10 @@
         <v>23</v>
       </c>
       <c r="D8" t="s">
+        <v>309</v>
+      </c>
+      <c r="E8" t="s">
         <v>310</v>
-      </c>
-      <c r="E8" t="s">
-        <v>311</v>
       </c>
       <c r="F8" t="s">
         <v>23</v>
@@ -4590,7 +4587,7 @@
         <v>25</v>
       </c>
       <c r="B9" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C9" t="s">
         <v>28</v>
@@ -4610,16 +4607,16 @@
         <v>29</v>
       </c>
       <c r="B10" t="s">
+        <v>291</v>
+      </c>
+      <c r="C10" t="s">
         <v>292</v>
       </c>
-      <c r="C10" t="s">
-        <v>293</v>
-      </c>
       <c r="D10" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F10" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="G10">
         <v>1</v>
@@ -4636,10 +4633,10 @@
         <v>10</v>
       </c>
       <c r="D11" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F11" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="G11">
         <v>1</v>
@@ -4737,7 +4734,7 @@
         <v>51</v>
       </c>
       <c r="D18" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="G18">
         <v>1</v>
@@ -4754,7 +4751,7 @@
         <v>53</v>
       </c>
       <c r="D19" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="G19">
         <v>1</v>
@@ -4785,16 +4782,16 @@
         <v>55</v>
       </c>
       <c r="B21" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C21" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D21" t="s">
         <v>27</v>
       </c>
       <c r="E21" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="G21">
         <v>1</v>
@@ -4816,13 +4813,13 @@
         <v>10</v>
       </c>
       <c r="D23" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="E23" t="s">
         <v>59</v>
       </c>
       <c r="F23" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="G23">
         <v>1</v>
@@ -4844,7 +4841,7 @@
         <v>63</v>
       </c>
       <c r="D25" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="G25">
         <v>1</v>
@@ -4861,7 +4858,7 @@
         <v>23</v>
       </c>
       <c r="D26" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="E26" t="s">
         <v>66</v>
@@ -4963,7 +4960,7 @@
         <v>76</v>
       </c>
       <c r="F32" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="G32">
         <v>1</v>
@@ -4974,7 +4971,7 @@
         <v>78</v>
       </c>
       <c r="F33" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="G33">
         <v>1</v>
@@ -4991,7 +4988,7 @@
         <v>80</v>
       </c>
       <c r="D34" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="G34">
         <v>1</v>
@@ -5008,7 +5005,7 @@
         <v>82</v>
       </c>
       <c r="D35" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="G35">
         <v>1</v>
@@ -5025,7 +5022,7 @@
         <v>84</v>
       </c>
       <c r="D36" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="G36">
         <v>1</v>
@@ -5042,7 +5039,7 @@
         <v>86</v>
       </c>
       <c r="D37" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="G37">
         <v>1</v>
@@ -5059,7 +5056,7 @@
         <v>88</v>
       </c>
       <c r="D38" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="G38">
         <v>1</v>
@@ -5076,7 +5073,7 @@
         <v>90</v>
       </c>
       <c r="D39" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="G39">
         <v>1</v>
@@ -5111,13 +5108,13 @@
         <v>97</v>
       </c>
       <c r="B43" t="s">
+        <v>314</v>
+      </c>
+      <c r="C43" t="s">
         <v>315</v>
       </c>
-      <c r="C43" t="s">
+      <c r="D43" t="s">
         <v>316</v>
-      </c>
-      <c r="D43" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
@@ -5332,7 +5329,7 @@
         <v>7</v>
       </c>
       <c r="F62" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="G62">
         <v>1</v>
@@ -5352,7 +5349,7 @@
         <v>7</v>
       </c>
       <c r="F63" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="G63">
         <v>1</v>
@@ -5372,7 +5369,7 @@
         <v>7</v>
       </c>
       <c r="F64" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="G64">
         <v>1</v>
@@ -5392,7 +5389,7 @@
         <v>7</v>
       </c>
       <c r="F65" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="G65">
         <v>1</v>
@@ -5624,10 +5621,10 @@
         <v>12</v>
       </c>
       <c r="D79" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F79" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="G79">
         <v>1</v>
@@ -5644,10 +5641,10 @@
         <v>14</v>
       </c>
       <c r="D80" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F80" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="G80">
         <v>1</v>
@@ -5667,7 +5664,7 @@
         <v>96</v>
       </c>
       <c r="E81" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F81" t="s">
         <v>23</v>
@@ -5731,10 +5728,10 @@
         <v>88</v>
       </c>
       <c r="D86" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E86" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="G86">
         <v>1</v>
@@ -5751,10 +5748,10 @@
         <v>90</v>
       </c>
       <c r="D87" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E87" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="G87">
         <v>1</v>
@@ -5771,10 +5768,10 @@
         <v>140</v>
       </c>
       <c r="D88" t="s">
+        <v>288</v>
+      </c>
+      <c r="E88" t="s">
         <v>289</v>
-      </c>
-      <c r="E88" t="s">
-        <v>290</v>
       </c>
       <c r="F88" t="s">
         <v>26</v>
@@ -5794,7 +5791,7 @@
         <v>153</v>
       </c>
       <c r="D89" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="E89" t="s">
         <v>153</v>
@@ -5814,7 +5811,7 @@
         <v>142</v>
       </c>
       <c r="D90" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="E90" t="s">
         <v>142</v>
@@ -5834,7 +5831,7 @@
         <v>28</v>
       </c>
       <c r="D91" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="E91" t="s">
         <v>28</v>
@@ -5854,7 +5851,7 @@
         <v>51</v>
       </c>
       <c r="D92" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G92">
         <v>1</v>
@@ -5959,7 +5956,7 @@
         <v>63</v>
       </c>
       <c r="D107" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G107">
         <v>1</v>
@@ -5991,7 +5988,7 @@
         <v>26</v>
       </c>
       <c r="D111" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E111" t="s">
         <v>194</v>
@@ -6014,7 +6011,7 @@
         <v>75</v>
       </c>
       <c r="D112" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G112">
         <v>1</v>
@@ -6141,7 +6138,7 @@
         <v>207</v>
       </c>
       <c r="F120" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="G120">
         <v>1</v>
@@ -6173,10 +6170,10 @@
         <v>6</v>
       </c>
       <c r="D124" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="F124" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="G124">
         <v>1</v>
@@ -6193,10 +6190,10 @@
         <v>10</v>
       </c>
       <c r="D125" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="F125" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="G125">
         <v>1</v>
@@ -6213,10 +6210,10 @@
         <v>12</v>
       </c>
       <c r="D126" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="F126" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="G126">
         <v>1</v>
@@ -6251,7 +6248,7 @@
         <v>7</v>
       </c>
       <c r="F130" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="G130">
         <v>1</v>
@@ -6276,7 +6273,7 @@
         <v>7</v>
       </c>
       <c r="F132" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="G132">
         <v>1</v>
@@ -6306,7 +6303,7 @@
         <v>7</v>
       </c>
       <c r="F135" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="G135">
         <v>1</v>
@@ -6326,7 +6323,7 @@
         <v>7</v>
       </c>
       <c r="F136" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="G136">
         <v>1</v>
@@ -6346,7 +6343,7 @@
         <v>7</v>
       </c>
       <c r="F137" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="G137">
         <v>1</v>
@@ -6368,10 +6365,10 @@
         <v>23</v>
       </c>
       <c r="D139" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="E139" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="F139" t="s">
         <v>23</v>

--- a/.doc/官方手册/引脚映射表.xlsx
+++ b/.doc/官方手册/引脚映射表.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\itgz2\Desktop\BetaRobot\.doc\官方手册\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB824936-890F-4EE1-A545-4534AB337648}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D0A116D-36F7-475A-8CEA-D5D22419D908}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DM_MC02" sheetId="1" r:id="rId1"/>
@@ -2727,7 +2727,7 @@
         <v>147</v>
       </c>
       <c r="B75" t="s">
-        <v>34</v>
+        <v>291</v>
       </c>
       <c r="C75" t="s">
         <v>6</v>
@@ -2807,7 +2807,7 @@
         <v>154</v>
       </c>
       <c r="B79" t="s">
-        <v>321</v>
+        <v>291</v>
       </c>
       <c r="C79" t="s">
         <v>12</v>
